--- a/SupplyDemandGPR.xlsx
+++ b/SupplyDemandGPR.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\w6504ys\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\w6504ys\GALILEO Dropbox\Yves Schüler\CoherentShock\Website\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{934F4B7B-05B8-4DDC-8C77-FB9F637BA6A7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DA11812D-9269-4BB8-88E2-1D84E740C1E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-18120" yWindow="-8295" windowWidth="18240" windowHeight="28320" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Readme" sheetId="1" r:id="rId1"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="20">
   <si>
     <t>Supply and demand geopolitical risk (GPR) indices</t>
   </si>
@@ -70,13 +70,25 @@
   <si>
     <t>Contact: yves.schueler (at) bundesbank.de</t>
   </si>
+  <si>
+    <t>ea_supply_gpr: additional supply-type GPR index (mean 100) for euro area</t>
+  </si>
+  <si>
+    <t>ea_demand_gpr: additional demand-type GPR index (mean 100) for euro area</t>
+  </si>
+  <si>
+    <t>ea_supply_gpr</t>
+  </si>
+  <si>
+    <t>ea_demand_GPR</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="165" formatCode="yyyy\-mm"/>
+    <numFmt numFmtId="164" formatCode="yyyy\-mm"/>
   </numFmts>
   <fonts count="5" x14ac:knownFonts="1">
     <font>
@@ -129,7 +141,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
@@ -138,8 +150,9 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="2" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="11" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Standard" xfId="0" builtinId="0"/>
@@ -442,7 +455,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:A20"/>
+  <dimension ref="A1:A22"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="120" customWidth="1"/>
@@ -514,23 +527,33 @@
       </c>
     </row>
     <row r="16" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A16" s="2"/>
+      <c r="A16" s="2" t="s">
+        <v>16</v>
+      </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A18" s="2"/>
+    </row>
+    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A19" s="2" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A18" s="2" t="s">
+    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A20" s="2" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A19" s="2"/>
-    </row>
-    <row r="20" spans="1:1" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A20" s="2" t="s">
+    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A21" s="2"/>
+    </row>
+    <row r="22" spans="1:1" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A22" s="2" t="s">
         <v>11</v>
       </c>
     </row>
@@ -541,13 +564,13 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:C496"/>
+  <dimension ref="A1:E496"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
         <v>12</v>
       </c>
@@ -557,8 +580,14 @@
       <c r="C1" s="3" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D1" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="4">
         <v>31048</v>
       </c>
@@ -569,7 +598,7 @@
         <v>44.330188486780898</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" s="4">
         <v>31079</v>
       </c>
@@ -580,7 +609,7 @@
         <v>58.2505026650188</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="4">
         <v>31107</v>
       </c>
@@ -591,7 +620,7 @@
         <v>75.975957677689095</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="4">
         <v>31138</v>
       </c>
@@ -602,7 +631,7 @@
         <v>41.646839482007401</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="4">
         <v>31168</v>
       </c>
@@ -613,7 +642,7 @@
         <v>90.840108162498296</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" s="4">
         <v>31199</v>
       </c>
@@ -624,7 +653,7 @@
         <v>113.358796575856</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" s="4">
         <v>31229</v>
       </c>
@@ -635,7 +664,7 @@
         <v>80.006023537485902</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" s="4">
         <v>31260</v>
       </c>
@@ -646,7 +675,7 @@
         <v>70.879192766364994</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" s="4">
         <v>31291</v>
       </c>
@@ -657,7 +686,7 @@
         <v>110.567746576429</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" s="4">
         <v>31321</v>
       </c>
@@ -668,7 +697,7 @@
         <v>126.91412315349</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" s="4">
         <v>31352</v>
       </c>
@@ -679,7 +708,7 @@
         <v>80.752215540377406</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" s="4">
         <v>31382</v>
       </c>
@@ -690,7 +719,7 @@
         <v>80.777573434877795</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" s="4">
         <v>31413</v>
       </c>
@@ -701,7 +730,7 @@
         <v>97.625289909800202</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" s="4">
         <v>31444</v>
       </c>
@@ -712,7 +741,7 @@
         <v>186.39824208107501</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" s="4">
         <v>31472</v>
       </c>
@@ -2131,7 +2160,7 @@
         <v>57.106332903213399</v>
       </c>
     </row>
-    <row r="145" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A145" s="4">
         <v>35400</v>
       </c>
@@ -2142,7 +2171,7 @@
         <v>59.721759360832401</v>
       </c>
     </row>
-    <row r="146" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A146" s="4">
         <v>35431</v>
       </c>
@@ -2153,7 +2182,7 @@
         <v>48.132307226778799</v>
       </c>
     </row>
-    <row r="147" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A147" s="4">
         <v>35462</v>
       </c>
@@ -2164,7 +2193,7 @@
         <v>35.5089249342846</v>
       </c>
     </row>
-    <row r="148" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A148" s="4">
         <v>35490</v>
       </c>
@@ -2175,7 +2204,7 @@
         <v>70.292391378142696</v>
       </c>
     </row>
-    <row r="149" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A149" s="4">
         <v>35521</v>
       </c>
@@ -2186,7 +2215,7 @@
         <v>24.364081229473801</v>
       </c>
     </row>
-    <row r="150" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A150" s="4">
         <v>35551</v>
       </c>
@@ -2197,7 +2226,7 @@
         <v>42.159828380738702</v>
       </c>
     </row>
-    <row r="151" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A151" s="4">
         <v>35582</v>
       </c>
@@ -2208,7 +2237,7 @@
         <v>34.443331205648903</v>
       </c>
     </row>
-    <row r="152" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A152" s="4">
         <v>35612</v>
       </c>
@@ -2219,7 +2248,7 @@
         <v>119.98271956971099</v>
       </c>
     </row>
-    <row r="153" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A153" s="4">
         <v>35643</v>
       </c>
@@ -2230,7 +2259,7 @@
         <v>79.9769953828376</v>
       </c>
     </row>
-    <row r="154" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A154" s="4">
         <v>35674</v>
       </c>
@@ -2241,7 +2270,7 @@
         <v>43.791399510476502</v>
       </c>
     </row>
-    <row r="155" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A155" s="4">
         <v>35704</v>
       </c>
@@ -2252,7 +2281,7 @@
         <v>35.329915629381503</v>
       </c>
     </row>
-    <row r="156" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A156" s="4">
         <v>35735</v>
       </c>
@@ -2263,7 +2292,7 @@
         <v>55.563910705153397</v>
       </c>
     </row>
-    <row r="157" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A157" s="4">
         <v>35765</v>
       </c>
@@ -2274,7 +2303,7 @@
         <v>13.754866744508</v>
       </c>
     </row>
-    <row r="158" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A158" s="4">
         <v>35796</v>
       </c>
@@ -2284,8 +2313,14 @@
       <c r="C158" s="5">
         <v>53.581298918961302</v>
       </c>
-    </row>
-    <row r="159" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D158">
+        <v>49.8294</v>
+      </c>
+      <c r="E158">
+        <v>96.5124</v>
+      </c>
+    </row>
+    <row r="159" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A159" s="4">
         <v>35827</v>
       </c>
@@ -2295,8 +2330,14 @@
       <c r="C159" s="5">
         <v>60.733359932789</v>
       </c>
-    </row>
-    <row r="160" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D159">
+        <v>56.561399999999999</v>
+      </c>
+      <c r="E159">
+        <v>124.5004</v>
+      </c>
+    </row>
+    <row r="160" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A160" s="4">
         <v>35855</v>
       </c>
@@ -2306,8 +2347,14 @@
       <c r="C160" s="5">
         <v>76.691906751504405</v>
       </c>
-    </row>
-    <row r="161" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D160">
+        <v>25.482299999999999</v>
+      </c>
+      <c r="E160">
+        <v>66.467600000000004</v>
+      </c>
+    </row>
+    <row r="161" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A161" s="4">
         <v>35886</v>
       </c>
@@ -2317,8 +2364,14 @@
       <c r="C161" s="5">
         <v>24.315280840904201</v>
       </c>
-    </row>
-    <row r="162" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D161">
+        <v>56.1479</v>
+      </c>
+      <c r="E161">
+        <v>54.2639</v>
+      </c>
+    </row>
+    <row r="162" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A162" s="4">
         <v>35916</v>
       </c>
@@ -2328,8 +2381,14 @@
       <c r="C162" s="5">
         <v>121.275606597709</v>
       </c>
-    </row>
-    <row r="163" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D162">
+        <v>33.990099999999998</v>
+      </c>
+      <c r="E162">
+        <v>70.959400000000002</v>
+      </c>
+    </row>
+    <row r="163" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A163" s="4">
         <v>35947</v>
       </c>
@@ -2339,8 +2398,14 @@
       <c r="C163" s="5">
         <v>104.21558359320299</v>
       </c>
-    </row>
-    <row r="164" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D163">
+        <v>55.100499999999997</v>
+      </c>
+      <c r="E163">
+        <v>132.447</v>
+      </c>
+    </row>
+    <row r="164" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A164" s="4">
         <v>35977</v>
       </c>
@@ -2350,8 +2415,14 @@
       <c r="C164" s="5">
         <v>61.475719081305101</v>
       </c>
-    </row>
-    <row r="165" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D164">
+        <v>47.650599999999997</v>
+      </c>
+      <c r="E164">
+        <v>90.197000000000003</v>
+      </c>
+    </row>
+    <row r="165" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A165" s="4">
         <v>36008</v>
       </c>
@@ -2361,8 +2432,14 @@
       <c r="C165" s="5">
         <v>134.89744692545699</v>
       </c>
-    </row>
-    <row r="166" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D165">
+        <v>46.006599999999999</v>
+      </c>
+      <c r="E165">
+        <v>81.555300000000003</v>
+      </c>
+    </row>
+    <row r="166" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A166" s="4">
         <v>36039</v>
       </c>
@@ -2372,8 +2449,14 @@
       <c r="C166" s="5">
         <v>59.464408046217997</v>
       </c>
-    </row>
-    <row r="167" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D166">
+        <v>29.832799999999999</v>
+      </c>
+      <c r="E166">
+        <v>74.168400000000005</v>
+      </c>
+    </row>
+    <row r="167" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A167" s="4">
         <v>36069</v>
       </c>
@@ -2383,8 +2466,14 @@
       <c r="C167" s="5">
         <v>74.171201771151601</v>
       </c>
-    </row>
-    <row r="168" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D167">
+        <v>31.632200000000001</v>
+      </c>
+      <c r="E167">
+        <v>41.1325</v>
+      </c>
+    </row>
+    <row r="168" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A168" s="4">
         <v>36100</v>
       </c>
@@ -2394,8 +2483,14 @@
       <c r="C168" s="5">
         <v>50.593739326046901</v>
       </c>
-    </row>
-    <row r="169" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D168">
+        <v>33.429699999999997</v>
+      </c>
+      <c r="E168">
+        <v>68.952699999999993</v>
+      </c>
+    </row>
+    <row r="169" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A169" s="4">
         <v>36130</v>
       </c>
@@ -2405,8 +2500,14 @@
       <c r="C169" s="5">
         <v>33.781967414479602</v>
       </c>
-    </row>
-    <row r="170" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D169">
+        <v>52.796199999999999</v>
+      </c>
+      <c r="E169">
+        <v>55.5914</v>
+      </c>
+    </row>
+    <row r="170" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A170" s="4">
         <v>36161</v>
       </c>
@@ -2416,8 +2517,14 @@
       <c r="C170" s="5">
         <v>63.199927709820003</v>
       </c>
-    </row>
-    <row r="171" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D170">
+        <v>66.737899999999996</v>
+      </c>
+      <c r="E170">
+        <v>56.457099999999997</v>
+      </c>
+    </row>
+    <row r="171" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A171" s="4">
         <v>36192</v>
       </c>
@@ -2427,8 +2534,14 @@
       <c r="C171" s="5">
         <v>50.061877734946599</v>
       </c>
-    </row>
-    <row r="172" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D171">
+        <v>46.631999999999998</v>
+      </c>
+      <c r="E171">
+        <v>49.786999999999999</v>
+      </c>
+    </row>
+    <row r="172" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A172" s="4">
         <v>36220</v>
       </c>
@@ -2438,8 +2551,14 @@
       <c r="C172" s="5">
         <v>113.976604836779</v>
       </c>
-    </row>
-    <row r="173" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D172">
+        <v>38.934399999999997</v>
+      </c>
+      <c r="E172">
+        <v>148.0573</v>
+      </c>
+    </row>
+    <row r="173" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A173" s="4">
         <v>36251</v>
       </c>
@@ -2449,8 +2568,14 @@
       <c r="C173" s="5">
         <v>68.123845736997794</v>
       </c>
-    </row>
-    <row r="174" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D173">
+        <v>248.8879</v>
+      </c>
+      <c r="E173">
+        <v>130.79079999999999</v>
+      </c>
+    </row>
+    <row r="174" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A174" s="4">
         <v>36281</v>
       </c>
@@ -2460,8 +2585,14 @@
       <c r="C174" s="5">
         <v>82.680252783301796</v>
       </c>
-    </row>
-    <row r="175" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D174">
+        <v>135.57149999999999</v>
+      </c>
+      <c r="E174">
+        <v>102.5137</v>
+      </c>
+    </row>
+    <row r="175" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A175" s="4">
         <v>36312</v>
       </c>
@@ -2471,8 +2602,14 @@
       <c r="C175" s="5">
         <v>75.353881993071994</v>
       </c>
-    </row>
-    <row r="176" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D175">
+        <v>55.297800000000002</v>
+      </c>
+      <c r="E175">
+        <v>70.563599999999994</v>
+      </c>
+    </row>
+    <row r="176" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A176" s="4">
         <v>36342</v>
       </c>
@@ -2482,8 +2619,14 @@
       <c r="C176" s="5">
         <v>75.772614531969396</v>
       </c>
-    </row>
-    <row r="177" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D176">
+        <v>56.569499999999998</v>
+      </c>
+      <c r="E176">
+        <v>174.9383</v>
+      </c>
+    </row>
+    <row r="177" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A177" s="4">
         <v>36373</v>
       </c>
@@ -2493,8 +2636,14 @@
       <c r="C177" s="5">
         <v>49.660414701253003</v>
       </c>
-    </row>
-    <row r="178" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D177">
+        <v>41.127899999999997</v>
+      </c>
+      <c r="E177">
+        <v>98.916700000000006</v>
+      </c>
+    </row>
+    <row r="178" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A178" s="4">
         <v>36404</v>
       </c>
@@ -2504,8 +2653,14 @@
       <c r="C178" s="5">
         <v>97.486931927101395</v>
       </c>
-    </row>
-    <row r="179" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D178">
+        <v>44.727200000000003</v>
+      </c>
+      <c r="E178">
+        <v>88.609899999999996</v>
+      </c>
+    </row>
+    <row r="179" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A179" s="4">
         <v>36434</v>
       </c>
@@ -2515,8 +2670,14 @@
       <c r="C179" s="5">
         <v>69.059854201445702</v>
       </c>
-    </row>
-    <row r="180" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D179">
+        <v>57.185200000000002</v>
+      </c>
+      <c r="E179">
+        <v>160.3398</v>
+      </c>
+    </row>
+    <row r="180" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A180" s="4">
         <v>36465</v>
       </c>
@@ -2526,8 +2687,14 @@
       <c r="C180" s="5">
         <v>47.090204767189697</v>
       </c>
-    </row>
-    <row r="181" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D180">
+        <v>44.112499999999997</v>
+      </c>
+      <c r="E180">
+        <v>62.880499999999998</v>
+      </c>
+    </row>
+    <row r="181" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A181" s="4">
         <v>36495</v>
       </c>
@@ -2537,8 +2704,14 @@
       <c r="C181" s="5">
         <v>39.8101959172945</v>
       </c>
-    </row>
-    <row r="182" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D181">
+        <v>64.633399999999995</v>
+      </c>
+      <c r="E181">
+        <v>38.779899999999998</v>
+      </c>
+    </row>
+    <row r="182" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A182" s="4">
         <v>36526</v>
       </c>
@@ -2548,8 +2721,14 @@
       <c r="C182" s="5">
         <v>27.8123635204911</v>
       </c>
-    </row>
-    <row r="183" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D182">
+        <v>57.548499999999997</v>
+      </c>
+      <c r="E182">
+        <v>50.240600000000001</v>
+      </c>
+    </row>
+    <row r="183" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A183" s="4">
         <v>36557</v>
       </c>
@@ -2559,8 +2738,14 @@
       <c r="C183" s="5">
         <v>85.227954058947205</v>
       </c>
-    </row>
-    <row r="184" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D183">
+        <v>55.8611</v>
+      </c>
+      <c r="E183">
+        <v>60.998800000000003</v>
+      </c>
+    </row>
+    <row r="184" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A184" s="4">
         <v>36586</v>
       </c>
@@ -2570,8 +2755,14 @@
       <c r="C184" s="5">
         <v>34.104431299105599</v>
       </c>
-    </row>
-    <row r="185" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D184">
+        <v>46.270299999999999</v>
+      </c>
+      <c r="E184">
+        <v>68.156499999999994</v>
+      </c>
+    </row>
+    <row r="185" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A185" s="4">
         <v>36617</v>
       </c>
@@ -2581,8 +2772,14 @@
       <c r="C185" s="5">
         <v>39.233757819431197</v>
       </c>
-    </row>
-    <row r="186" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D185">
+        <v>34.400599999999997</v>
+      </c>
+      <c r="E185">
+        <v>19.185500000000001</v>
+      </c>
+    </row>
+    <row r="186" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A186" s="4">
         <v>36647</v>
       </c>
@@ -2592,8 +2789,14 @@
       <c r="C186" s="5">
         <v>75.168181624191106</v>
       </c>
-    </row>
-    <row r="187" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D186">
+        <v>55.986699999999999</v>
+      </c>
+      <c r="E186">
+        <v>90.485500000000002</v>
+      </c>
+    </row>
+    <row r="187" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A187" s="4">
         <v>36678</v>
       </c>
@@ -2603,8 +2806,14 @@
       <c r="C187" s="5">
         <v>49.012333673693803</v>
       </c>
-    </row>
-    <row r="188" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D187">
+        <v>34.455399999999997</v>
+      </c>
+      <c r="E187">
+        <v>49.641100000000002</v>
+      </c>
+    </row>
+    <row r="188" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A188" s="4">
         <v>36708</v>
       </c>
@@ -2614,8 +2823,14 @@
       <c r="C188" s="5">
         <v>39.686773023577899</v>
       </c>
-    </row>
-    <row r="189" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D188">
+        <v>42.623199999999997</v>
+      </c>
+      <c r="E188">
+        <v>77.618899999999996</v>
+      </c>
+    </row>
+    <row r="189" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A189" s="4">
         <v>36739</v>
       </c>
@@ -2625,8 +2840,14 @@
       <c r="C189" s="5">
         <v>31.314888591291101</v>
       </c>
-    </row>
-    <row r="190" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D189">
+        <v>74.254099999999994</v>
+      </c>
+      <c r="E189">
+        <v>56.192399999999999</v>
+      </c>
+    </row>
+    <row r="190" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A190" s="4">
         <v>36770</v>
       </c>
@@ -2636,8 +2857,14 @@
       <c r="C190" s="5">
         <v>76.529602835936402</v>
       </c>
-    </row>
-    <row r="191" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D190">
+        <v>156.81190000000001</v>
+      </c>
+      <c r="E190">
+        <v>53.568399999999997</v>
+      </c>
+    </row>
+    <row r="191" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A191" s="4">
         <v>36800</v>
       </c>
@@ -2647,8 +2874,14 @@
       <c r="C191" s="5">
         <v>65.008385882611293</v>
       </c>
-    </row>
-    <row r="192" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D191">
+        <v>116.04649999999999</v>
+      </c>
+      <c r="E191">
+        <v>107.7726</v>
+      </c>
+    </row>
+    <row r="192" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A192" s="4">
         <v>36831</v>
       </c>
@@ -2658,8 +2891,14 @@
       <c r="C192" s="5">
         <v>38.531287020120402</v>
       </c>
-    </row>
-    <row r="193" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D192">
+        <v>54.448099999999997</v>
+      </c>
+      <c r="E192">
+        <v>66.322900000000004</v>
+      </c>
+    </row>
+    <row r="193" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A193" s="4">
         <v>36861</v>
       </c>
@@ -2669,8 +2908,14 @@
       <c r="C193" s="5">
         <v>32.336810270606897</v>
       </c>
-    </row>
-    <row r="194" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D193">
+        <v>40.231400000000001</v>
+      </c>
+      <c r="E193">
+        <v>44.768500000000003</v>
+      </c>
+    </row>
+    <row r="194" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A194" s="4">
         <v>36892</v>
       </c>
@@ -2680,8 +2925,14 @@
       <c r="C194" s="5">
         <v>24.297472081380601</v>
       </c>
-    </row>
-    <row r="195" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D194">
+        <v>37.664000000000001</v>
+      </c>
+      <c r="E194">
+        <v>33.7318</v>
+      </c>
+    </row>
+    <row r="195" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A195" s="4">
         <v>36923</v>
       </c>
@@ -2691,8 +2942,14 @@
       <c r="C195" s="5">
         <v>49.333580798313101</v>
       </c>
-    </row>
-    <row r="196" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D195">
+        <v>43.1295</v>
+      </c>
+      <c r="E195">
+        <v>49.528799999999997</v>
+      </c>
+    </row>
+    <row r="196" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A196" s="4">
         <v>36951</v>
       </c>
@@ -2702,8 +2959,14 @@
       <c r="C196" s="5">
         <v>41.998013840934597</v>
       </c>
-    </row>
-    <row r="197" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D196">
+        <v>46.725999999999999</v>
+      </c>
+      <c r="E196">
+        <v>150.9246</v>
+      </c>
+    </row>
+    <row r="197" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A197" s="4">
         <v>36982</v>
       </c>
@@ -2713,8 +2976,14 @@
       <c r="C197" s="5">
         <v>26.441673702465401</v>
       </c>
-    </row>
-    <row r="198" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D197">
+        <v>58.037700000000001</v>
+      </c>
+      <c r="E197">
+        <v>93.617199999999997</v>
+      </c>
+    </row>
+    <row r="198" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A198" s="4">
         <v>37012</v>
       </c>
@@ -2724,8 +2993,14 @@
       <c r="C198" s="5">
         <v>44.417187616563801</v>
       </c>
-    </row>
-    <row r="199" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D198">
+        <v>47.818899999999999</v>
+      </c>
+      <c r="E198">
+        <v>62.4895</v>
+      </c>
+    </row>
+    <row r="199" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A199" s="4">
         <v>37043</v>
       </c>
@@ -2735,8 +3010,14 @@
       <c r="C199" s="5">
         <v>33.561827350104402</v>
       </c>
-    </row>
-    <row r="200" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D199">
+        <v>63.996299999999998</v>
+      </c>
+      <c r="E199">
+        <v>83.796599999999998</v>
+      </c>
+    </row>
+    <row r="200" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A200" s="4">
         <v>37073</v>
       </c>
@@ -2746,8 +3027,14 @@
       <c r="C200" s="5">
         <v>54.7457943321212</v>
       </c>
-    </row>
-    <row r="201" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D200">
+        <v>55.998699999999999</v>
+      </c>
+      <c r="E200">
+        <v>98.305099999999996</v>
+      </c>
+    </row>
+    <row r="201" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A201" s="4">
         <v>37104</v>
       </c>
@@ -2757,8 +3044,14 @@
       <c r="C201" s="5">
         <v>50.959475744286799</v>
       </c>
-    </row>
-    <row r="202" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D201">
+        <v>61.520400000000002</v>
+      </c>
+      <c r="E201">
+        <v>76.179900000000004</v>
+      </c>
+    </row>
+    <row r="202" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A202" s="4">
         <v>37135</v>
       </c>
@@ -2768,8 +3061,14 @@
       <c r="C202" s="5">
         <v>1509.16391697012</v>
       </c>
-    </row>
-    <row r="203" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D202">
+        <v>227.1549</v>
+      </c>
+      <c r="E202">
+        <v>608.89409999999998</v>
+      </c>
+    </row>
+    <row r="203" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A203" s="4">
         <v>37165</v>
       </c>
@@ -2779,8 +3078,14 @@
       <c r="C203" s="5">
         <v>1597.32250924244</v>
       </c>
-    </row>
-    <row r="204" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D203">
+        <v>117.21169999999999</v>
+      </c>
+      <c r="E203">
+        <v>454.34</v>
+      </c>
+    </row>
+    <row r="204" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A204" s="4">
         <v>37196</v>
       </c>
@@ -2790,8 +3095,14 @@
       <c r="C204" s="5">
         <v>856.26086331421504</v>
       </c>
-    </row>
-    <row r="205" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D204">
+        <v>57.636699999999998</v>
+      </c>
+      <c r="E204">
+        <v>192.30549999999999</v>
+      </c>
+    </row>
+    <row r="205" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A205" s="4">
         <v>37226</v>
       </c>
@@ -2801,8 +3112,14 @@
       <c r="C205" s="5">
         <v>428.362395751951</v>
       </c>
-    </row>
-    <row r="206" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D205">
+        <v>50.009399999999999</v>
+      </c>
+      <c r="E205">
+        <v>124.6623</v>
+      </c>
+    </row>
+    <row r="206" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A206" s="4">
         <v>37257</v>
       </c>
@@ -2812,8 +3129,14 @@
       <c r="C206" s="5">
         <v>255.43651910345</v>
       </c>
-    </row>
-    <row r="207" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D206">
+        <v>53.1753</v>
+      </c>
+      <c r="E206">
+        <v>100.3497</v>
+      </c>
+    </row>
+    <row r="207" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A207" s="4">
         <v>37288</v>
       </c>
@@ -2823,8 +3146,14 @@
       <c r="C207" s="5">
         <v>191.337859081441</v>
       </c>
-    </row>
-    <row r="208" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D207">
+        <v>38.239899999999999</v>
+      </c>
+      <c r="E207">
+        <v>61.828600000000002</v>
+      </c>
+    </row>
+    <row r="208" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A208" s="4">
         <v>37316</v>
       </c>
@@ -2834,8 +3163,14 @@
       <c r="C208" s="5">
         <v>150.216113311871</v>
       </c>
-    </row>
-    <row r="209" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D208">
+        <v>49.791499999999999</v>
+      </c>
+      <c r="E208">
+        <v>78.180800000000005</v>
+      </c>
+    </row>
+    <row r="209" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A209" s="4">
         <v>37347</v>
       </c>
@@ -2845,8 +3180,14 @@
       <c r="C209" s="5">
         <v>203.111772484108</v>
       </c>
-    </row>
-    <row r="210" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D209">
+        <v>118.6861</v>
+      </c>
+      <c r="E209">
+        <v>93.467600000000004</v>
+      </c>
+    </row>
+    <row r="210" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A210" s="4">
         <v>37377</v>
       </c>
@@ -2856,8 +3197,14 @@
       <c r="C210" s="5">
         <v>228.574227332243</v>
       </c>
-    </row>
-    <row r="211" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D210">
+        <v>62.220399999999998</v>
+      </c>
+      <c r="E210">
+        <v>84.916499999999999</v>
+      </c>
+    </row>
+    <row r="211" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A211" s="4">
         <v>37408</v>
       </c>
@@ -2867,8 +3214,14 @@
       <c r="C211" s="5">
         <v>261.70574531430498</v>
       </c>
-    </row>
-    <row r="212" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D211">
+        <v>63.4315</v>
+      </c>
+      <c r="E211">
+        <v>104.70610000000001</v>
+      </c>
+    </row>
+    <row r="212" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A212" s="4">
         <v>37438</v>
       </c>
@@ -2878,8 +3231,14 @@
       <c r="C212" s="5">
         <v>182.028067342599</v>
       </c>
-    </row>
-    <row r="213" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D212">
+        <v>49.3048</v>
+      </c>
+      <c r="E212">
+        <v>106.7056</v>
+      </c>
+    </row>
+    <row r="213" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A213" s="4">
         <v>37469</v>
       </c>
@@ -2889,8 +3248,14 @@
       <c r="C213" s="5">
         <v>198.00088759783901</v>
       </c>
-    </row>
-    <row r="214" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D213">
+        <v>115.57510000000001</v>
+      </c>
+      <c r="E213">
+        <v>148.92840000000001</v>
+      </c>
+    </row>
+    <row r="214" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A214" s="4">
         <v>37500</v>
       </c>
@@ -2900,8 +3265,14 @@
       <c r="C214" s="5">
         <v>230.661302709804</v>
       </c>
-    </row>
-    <row r="215" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D214">
+        <v>130.19630000000001</v>
+      </c>
+      <c r="E214">
+        <v>155.6807</v>
+      </c>
+    </row>
+    <row r="215" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A215" s="4">
         <v>37530</v>
       </c>
@@ -2911,8 +3282,14 @@
       <c r="C215" s="5">
         <v>256.367187432771</v>
       </c>
-    </row>
-    <row r="216" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D215">
+        <v>98.716499999999996</v>
+      </c>
+      <c r="E215">
+        <v>175.26650000000001</v>
+      </c>
+    </row>
+    <row r="216" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A216" s="4">
         <v>37561</v>
       </c>
@@ -2922,8 +3299,14 @@
       <c r="C216" s="5">
         <v>142.821984965898</v>
       </c>
-    </row>
-    <row r="217" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D216">
+        <v>52.911200000000001</v>
+      </c>
+      <c r="E216">
+        <v>115.3892</v>
+      </c>
+    </row>
+    <row r="217" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A217" s="4">
         <v>37591</v>
       </c>
@@ -2933,8 +3316,14 @@
       <c r="C217" s="5">
         <v>181.29991193871001</v>
       </c>
-    </row>
-    <row r="218" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D217">
+        <v>235.01490000000001</v>
+      </c>
+      <c r="E217">
+        <v>150.53139999999999</v>
+      </c>
+    </row>
+    <row r="218" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A218" s="4">
         <v>37622</v>
       </c>
@@ -2944,8 +3333,14 @@
       <c r="C218" s="5">
         <v>284.46118718420098</v>
       </c>
-    </row>
-    <row r="219" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D218">
+        <v>186.74199999999999</v>
+      </c>
+      <c r="E218">
+        <v>301.56779999999998</v>
+      </c>
+    </row>
+    <row r="219" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A219" s="4">
         <v>37653</v>
       </c>
@@ -2955,8 +3350,14 @@
       <c r="C219" s="5">
         <v>264.38726480990198</v>
       </c>
-    </row>
-    <row r="220" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D219">
+        <v>240.084</v>
+      </c>
+      <c r="E219">
+        <v>442.04180000000002</v>
+      </c>
+    </row>
+    <row r="220" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A220" s="4">
         <v>37681</v>
       </c>
@@ -2966,8 +3367,14 @@
       <c r="C220" s="5">
         <v>430.69527139251102</v>
       </c>
-    </row>
-    <row r="221" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D220">
+        <v>267.00560000000002</v>
+      </c>
+      <c r="E220">
+        <v>473.46570000000003</v>
+      </c>
+    </row>
+    <row r="221" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A221" s="4">
         <v>37712</v>
       </c>
@@ -2977,8 +3384,14 @@
       <c r="C221" s="5">
         <v>305.80709762249199</v>
       </c>
-    </row>
-    <row r="222" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D221">
+        <v>109.50579999999999</v>
+      </c>
+      <c r="E221">
+        <v>253.56319999999999</v>
+      </c>
+    </row>
+    <row r="222" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A222" s="4">
         <v>37742</v>
       </c>
@@ -2988,8 +3401,14 @@
       <c r="C222" s="5">
         <v>192.37358873426501</v>
       </c>
-    </row>
-    <row r="223" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D222">
+        <v>47.477499999999999</v>
+      </c>
+      <c r="E222">
+        <v>115.5159</v>
+      </c>
+    </row>
+    <row r="223" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A223" s="4">
         <v>37773</v>
       </c>
@@ -2999,8 +3418,14 @@
       <c r="C223" s="5">
         <v>182.317866314675</v>
       </c>
-    </row>
-    <row r="224" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D223">
+        <v>55.465699999999998</v>
+      </c>
+      <c r="E223">
+        <v>93.428600000000003</v>
+      </c>
+    </row>
+    <row r="224" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A224" s="4">
         <v>37803</v>
       </c>
@@ -3010,8 +3435,14 @@
       <c r="C224" s="5">
         <v>211.62922508614699</v>
       </c>
-    </row>
-    <row r="225" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D224">
+        <v>87.811000000000007</v>
+      </c>
+      <c r="E224">
+        <v>97.721900000000005</v>
+      </c>
+    </row>
+    <row r="225" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A225" s="4">
         <v>37834</v>
       </c>
@@ -3021,8 +3452,14 @@
       <c r="C225" s="5">
         <v>173.110913823457</v>
       </c>
-    </row>
-    <row r="226" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D225">
+        <v>127.398</v>
+      </c>
+      <c r="E225">
+        <v>157.56110000000001</v>
+      </c>
+    </row>
+    <row r="226" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A226" s="4">
         <v>37865</v>
       </c>
@@ -3032,8 +3469,14 @@
       <c r="C226" s="5">
         <v>91.599084262745805</v>
       </c>
-    </row>
-    <row r="227" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D226">
+        <v>76.936099999999996</v>
+      </c>
+      <c r="E226">
+        <v>109.6386</v>
+      </c>
+    </row>
+    <row r="227" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A227" s="4">
         <v>37895</v>
       </c>
@@ -3043,8 +3486,14 @@
       <c r="C227" s="5">
         <v>90.278968928203597</v>
       </c>
-    </row>
-    <row r="228" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D227">
+        <v>63.680199999999999</v>
+      </c>
+      <c r="E227">
+        <v>121.352</v>
+      </c>
+    </row>
+    <row r="228" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A228" s="4">
         <v>37926</v>
       </c>
@@ -3054,8 +3503,14 @@
       <c r="C228" s="5">
         <v>119.13368492734899</v>
       </c>
-    </row>
-    <row r="229" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D228">
+        <v>58.576700000000002</v>
+      </c>
+      <c r="E228">
+        <v>115.80159999999999</v>
+      </c>
+    </row>
+    <row r="229" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A229" s="4">
         <v>37956</v>
       </c>
@@ -3065,8 +3520,14 @@
       <c r="C229" s="5">
         <v>117.316961641571</v>
       </c>
-    </row>
-    <row r="230" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D229">
+        <v>59.613300000000002</v>
+      </c>
+      <c r="E229">
+        <v>57.533000000000001</v>
+      </c>
+    </row>
+    <row r="230" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A230" s="4">
         <v>37987</v>
       </c>
@@ -3076,8 +3537,14 @@
       <c r="C230" s="5">
         <v>59.636893655254497</v>
       </c>
-    </row>
-    <row r="231" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D230">
+        <v>70.753500000000003</v>
+      </c>
+      <c r="E230">
+        <v>65.306899999999999</v>
+      </c>
+    </row>
+    <row r="231" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A231" s="4">
         <v>38018</v>
       </c>
@@ -3087,8 +3554,14 @@
       <c r="C231" s="5">
         <v>129.281531697551</v>
       </c>
-    </row>
-    <row r="232" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D231">
+        <v>25.8491</v>
+      </c>
+      <c r="E231">
+        <v>103.8943</v>
+      </c>
+    </row>
+    <row r="232" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A232" s="4">
         <v>38047</v>
       </c>
@@ -3098,8 +3571,14 @@
       <c r="C232" s="5">
         <v>156.075025421166</v>
       </c>
-    </row>
-    <row r="233" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D232">
+        <v>89.483900000000006</v>
+      </c>
+      <c r="E232">
+        <v>174.4803</v>
+      </c>
+    </row>
+    <row r="233" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A233" s="4">
         <v>38078</v>
       </c>
@@ -3109,8 +3588,14 @@
       <c r="C233" s="5">
         <v>143.06587983142001</v>
       </c>
-    </row>
-    <row r="234" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D233">
+        <v>126.6994</v>
+      </c>
+      <c r="E233">
+        <v>98.999799999999993</v>
+      </c>
+    </row>
+    <row r="234" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A234" s="4">
         <v>38108</v>
       </c>
@@ -3120,8 +3605,14 @@
       <c r="C234" s="5">
         <v>197.597991293517</v>
       </c>
-    </row>
-    <row r="235" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D234">
+        <v>190.2714</v>
+      </c>
+      <c r="E234">
+        <v>96.588800000000006</v>
+      </c>
+    </row>
+    <row r="235" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A235" s="4">
         <v>38139</v>
       </c>
@@ -3131,8 +3622,14 @@
       <c r="C235" s="5">
         <v>102.102561702014</v>
       </c>
-    </row>
-    <row r="236" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D235">
+        <v>125.6799</v>
+      </c>
+      <c r="E235">
+        <v>79.540000000000006</v>
+      </c>
+    </row>
+    <row r="236" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A236" s="4">
         <v>38169</v>
       </c>
@@ -3142,8 +3639,14 @@
       <c r="C236" s="5">
         <v>71.436222794198898</v>
       </c>
-    </row>
-    <row r="237" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D236">
+        <v>59.446800000000003</v>
+      </c>
+      <c r="E236">
+        <v>49.750500000000002</v>
+      </c>
+    </row>
+    <row r="237" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A237" s="4">
         <v>38200</v>
       </c>
@@ -3153,8 +3656,14 @@
       <c r="C237" s="5">
         <v>178.70786673426301</v>
       </c>
-    </row>
-    <row r="238" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D237">
+        <v>218.07640000000001</v>
+      </c>
+      <c r="E237">
+        <v>96.912999999999997</v>
+      </c>
+    </row>
+    <row r="238" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A238" s="4">
         <v>38231</v>
       </c>
@@ -3164,8 +3673,14 @@
       <c r="C238" s="5">
         <v>107.46366214239001</v>
       </c>
-    </row>
-    <row r="239" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D238">
+        <v>133.87639999999999</v>
+      </c>
+      <c r="E238">
+        <v>142.91640000000001</v>
+      </c>
+    </row>
+    <row r="239" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A239" s="4">
         <v>38261</v>
       </c>
@@ -3175,8 +3690,14 @@
       <c r="C239" s="5">
         <v>85.305670328842297</v>
       </c>
-    </row>
-    <row r="240" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D239">
+        <v>88.7256</v>
+      </c>
+      <c r="E239">
+        <v>57.037399999999998</v>
+      </c>
+    </row>
+    <row r="240" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A240" s="4">
         <v>38292</v>
       </c>
@@ -3186,8 +3707,14 @@
       <c r="C240" s="5">
         <v>104.121303517464</v>
       </c>
-    </row>
-    <row r="241" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D240">
+        <v>46.511499999999998</v>
+      </c>
+      <c r="E240">
+        <v>107.56019999999999</v>
+      </c>
+    </row>
+    <row r="241" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A241" s="4">
         <v>38322</v>
       </c>
@@ -3197,8 +3724,14 @@
       <c r="C241" s="5">
         <v>91.326795595984805</v>
       </c>
-    </row>
-    <row r="242" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D241">
+        <v>53.813099999999999</v>
+      </c>
+      <c r="E241">
+        <v>42.569499999999998</v>
+      </c>
+    </row>
+    <row r="242" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A242" s="4">
         <v>38353</v>
       </c>
@@ -3208,8 +3741,14 @@
       <c r="C242" s="5">
         <v>78.817116716159603</v>
       </c>
-    </row>
-    <row r="243" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D242">
+        <v>66.061000000000007</v>
+      </c>
+      <c r="E242">
+        <v>48.1389</v>
+      </c>
+    </row>
+    <row r="243" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A243" s="4">
         <v>38384</v>
       </c>
@@ -3219,8 +3758,14 @@
       <c r="C243" s="5">
         <v>34.089113385694503</v>
       </c>
-    </row>
-    <row r="244" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D243">
+        <v>20.508099999999999</v>
+      </c>
+      <c r="E243">
+        <v>53.3887</v>
+      </c>
+    </row>
+    <row r="244" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A244" s="4">
         <v>38412</v>
       </c>
@@ -3230,8 +3775,14 @@
       <c r="C244" s="5">
         <v>67.877760652274006</v>
       </c>
-    </row>
-    <row r="245" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D244">
+        <v>48.683999999999997</v>
+      </c>
+      <c r="E244">
+        <v>45.0349</v>
+      </c>
+    </row>
+    <row r="245" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A245" s="4">
         <v>38443</v>
       </c>
@@ -3241,8 +3792,14 @@
       <c r="C245" s="5">
         <v>80.454647988971104</v>
       </c>
-    </row>
-    <row r="246" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D245">
+        <v>48.983699999999999</v>
+      </c>
+      <c r="E245">
+        <v>39.552500000000002</v>
+      </c>
+    </row>
+    <row r="246" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A246" s="4">
         <v>38473</v>
       </c>
@@ -3252,8 +3809,14 @@
       <c r="C246" s="5">
         <v>67.928842687560802</v>
       </c>
-    </row>
-    <row r="247" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D246">
+        <v>43.106699999999996</v>
+      </c>
+      <c r="E246">
+        <v>93.265600000000006</v>
+      </c>
+    </row>
+    <row r="247" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A247" s="4">
         <v>38504</v>
       </c>
@@ -3263,8 +3826,14 @@
       <c r="C247" s="5">
         <v>60.697101023029397</v>
       </c>
-    </row>
-    <row r="248" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D247">
+        <v>62.097099999999998</v>
+      </c>
+      <c r="E247">
+        <v>59.048000000000002</v>
+      </c>
+    </row>
+    <row r="248" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A248" s="4">
         <v>38534</v>
       </c>
@@ -3274,8 +3843,14 @@
       <c r="C248" s="5">
         <v>137.30347974445101</v>
       </c>
-    </row>
-    <row r="249" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D248">
+        <v>57.549900000000001</v>
+      </c>
+      <c r="E248">
+        <v>97.379900000000006</v>
+      </c>
+    </row>
+    <row r="249" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A249" s="4">
         <v>38565</v>
       </c>
@@ -3285,8 +3860,14 @@
       <c r="C249" s="5">
         <v>100.96604037492099</v>
       </c>
-    </row>
-    <row r="250" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D249">
+        <v>154.5643</v>
+      </c>
+      <c r="E249">
+        <v>37.6248</v>
+      </c>
+    </row>
+    <row r="250" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A250" s="4">
         <v>38596</v>
       </c>
@@ -3296,8 +3877,14 @@
       <c r="C250" s="5">
         <v>85.289090562522304</v>
       </c>
-    </row>
-    <row r="251" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D250">
+        <v>65.714500000000001</v>
+      </c>
+      <c r="E250">
+        <v>67.370099999999994</v>
+      </c>
+    </row>
+    <row r="251" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A251" s="4">
         <v>38626</v>
       </c>
@@ -3307,8 +3894,14 @@
       <c r="C251" s="5">
         <v>50.173595030929597</v>
       </c>
-    </row>
-    <row r="252" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D251">
+        <v>69.856899999999996</v>
+      </c>
+      <c r="E251">
+        <v>95.173900000000003</v>
+      </c>
+    </row>
+    <row r="252" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A252" s="4">
         <v>38657</v>
       </c>
@@ -3318,8 +3911,14 @@
       <c r="C252" s="5">
         <v>71.3902294391265</v>
       </c>
-    </row>
-    <row r="253" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D252">
+        <v>53.003999999999998</v>
+      </c>
+      <c r="E252">
+        <v>51.941400000000002</v>
+      </c>
+    </row>
+    <row r="253" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A253" s="4">
         <v>38687</v>
       </c>
@@ -3329,8 +3928,14 @@
       <c r="C253" s="5">
         <v>78.802673190445205</v>
       </c>
-    </row>
-    <row r="254" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D253">
+        <v>29.0062</v>
+      </c>
+      <c r="E253">
+        <v>61.316000000000003</v>
+      </c>
+    </row>
+    <row r="254" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A254" s="4">
         <v>38718</v>
       </c>
@@ -3340,8 +3945,14 @@
       <c r="C254" s="5">
         <v>63.029816712322699</v>
       </c>
-    </row>
-    <row r="255" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D254">
+        <v>159.43639999999999</v>
+      </c>
+      <c r="E254">
+        <v>78.800299999999993</v>
+      </c>
+    </row>
+    <row r="255" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A255" s="4">
         <v>38749</v>
       </c>
@@ -3351,8 +3962,14 @@
       <c r="C255" s="5">
         <v>58.485357989224298</v>
       </c>
-    </row>
-    <row r="256" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D255">
+        <v>57.184699999999999</v>
+      </c>
+      <c r="E255">
+        <v>57.575099999999999</v>
+      </c>
+    </row>
+    <row r="256" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A256" s="4">
         <v>38777</v>
       </c>
@@ -3362,8 +3979,14 @@
       <c r="C256" s="5">
         <v>54.012449090293003</v>
       </c>
-    </row>
-    <row r="257" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D256">
+        <v>59.121200000000002</v>
+      </c>
+      <c r="E256">
+        <v>36.148899999999998</v>
+      </c>
+    </row>
+    <row r="257" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A257" s="4">
         <v>38808</v>
       </c>
@@ -3373,8 +3996,14 @@
       <c r="C257" s="5">
         <v>81.987360492315801</v>
       </c>
-    </row>
-    <row r="258" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D257">
+        <v>167.036</v>
+      </c>
+      <c r="E257">
+        <v>56.057600000000001</v>
+      </c>
+    </row>
+    <row r="258" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A258" s="4">
         <v>38838</v>
       </c>
@@ -3384,8 +4013,14 @@
       <c r="C258" s="5">
         <v>48.824229906512301</v>
       </c>
-    </row>
-    <row r="259" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D258">
+        <v>61.887700000000002</v>
+      </c>
+      <c r="E258">
+        <v>60.7988</v>
+      </c>
+    </row>
+    <row r="259" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A259" s="4">
         <v>38869</v>
       </c>
@@ -3395,8 +4030,14 @@
       <c r="C259" s="5">
         <v>83.052284910444996</v>
       </c>
-    </row>
-    <row r="260" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D259">
+        <v>62.9758</v>
+      </c>
+      <c r="E259">
+        <v>56.113199999999999</v>
+      </c>
+    </row>
+    <row r="260" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A260" s="4">
         <v>38899</v>
       </c>
@@ -3406,8 +4047,14 @@
       <c r="C260" s="5">
         <v>68.856280039454603</v>
       </c>
-    </row>
-    <row r="261" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D260">
+        <v>160.1516</v>
+      </c>
+      <c r="E260">
+        <v>130.6446</v>
+      </c>
+    </row>
+    <row r="261" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A261" s="4">
         <v>38930</v>
       </c>
@@ -3417,8 +4064,14 @@
       <c r="C261" s="5">
         <v>154.57736307696601</v>
       </c>
-    </row>
-    <row r="262" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D261">
+        <v>184.631</v>
+      </c>
+      <c r="E261">
+        <v>173.04300000000001</v>
+      </c>
+    </row>
+    <row r="262" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A262" s="4">
         <v>38961</v>
       </c>
@@ -3428,8 +4081,14 @@
       <c r="C262" s="5">
         <v>97.368235865581099</v>
       </c>
-    </row>
-    <row r="263" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D262">
+        <v>53.840499999999999</v>
+      </c>
+      <c r="E262">
+        <v>68.218500000000006</v>
+      </c>
+    </row>
+    <row r="263" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A263" s="4">
         <v>38991</v>
       </c>
@@ -3439,8 +4098,14 @@
       <c r="C263" s="5">
         <v>128.18072876494401</v>
       </c>
-    </row>
-    <row r="264" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D263">
+        <v>40.664999999999999</v>
+      </c>
+      <c r="E263">
+        <v>40.475499999999997</v>
+      </c>
+    </row>
+    <row r="264" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A264" s="4">
         <v>39022</v>
       </c>
@@ -3450,8 +4115,14 @@
       <c r="C264" s="5">
         <v>70.422514657854705</v>
       </c>
-    </row>
-    <row r="265" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D264">
+        <v>59.883699999999997</v>
+      </c>
+      <c r="E264">
+        <v>45.3765</v>
+      </c>
+    </row>
+    <row r="265" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A265" s="4">
         <v>39052</v>
       </c>
@@ -3461,8 +4132,14 @@
       <c r="C265" s="5">
         <v>81.406914849277996</v>
       </c>
-    </row>
-    <row r="266" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D265">
+        <v>46.849800000000002</v>
+      </c>
+      <c r="E265">
+        <v>42.571300000000001</v>
+      </c>
+    </row>
+    <row r="266" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A266" s="4">
         <v>39083</v>
       </c>
@@ -3472,8 +4149,14 @@
       <c r="C266" s="5">
         <v>64.827797539169396</v>
       </c>
-    </row>
-    <row r="267" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D266">
+        <v>82.282300000000006</v>
+      </c>
+      <c r="E266">
+        <v>48.277200000000001</v>
+      </c>
+    </row>
+    <row r="267" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A267" s="4">
         <v>39114</v>
       </c>
@@ -3483,8 +4166,14 @@
       <c r="C267" s="5">
         <v>61.140563994719201</v>
       </c>
-    </row>
-    <row r="268" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D267">
+        <v>61.750999999999998</v>
+      </c>
+      <c r="E267">
+        <v>39.281999999999996</v>
+      </c>
+    </row>
+    <row r="268" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A268" s="4">
         <v>39142</v>
       </c>
@@ -3494,8 +4183,14 @@
       <c r="C268" s="5">
         <v>69.387932615998295</v>
       </c>
-    </row>
-    <row r="269" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D268">
+        <v>63.0276</v>
+      </c>
+      <c r="E268">
+        <v>38.068100000000001</v>
+      </c>
+    </row>
+    <row r="269" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A269" s="4">
         <v>39173</v>
       </c>
@@ -3505,8 +4200,14 @@
       <c r="C269" s="5">
         <v>50.4804879249021</v>
       </c>
-    </row>
-    <row r="270" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D269">
+        <v>39.4985</v>
+      </c>
+      <c r="E269">
+        <v>51.037799999999997</v>
+      </c>
+    </row>
+    <row r="270" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A270" s="4">
         <v>39203</v>
       </c>
@@ -3516,8 +4217,14 @@
       <c r="C270" s="5">
         <v>70.614970381219393</v>
       </c>
-    </row>
-    <row r="271" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D270">
+        <v>62.116500000000002</v>
+      </c>
+      <c r="E270">
+        <v>55.888100000000001</v>
+      </c>
+    </row>
+    <row r="271" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A271" s="4">
         <v>39234</v>
       </c>
@@ -3527,8 +4234,14 @@
       <c r="C271" s="5">
         <v>78.211912936519198</v>
       </c>
-    </row>
-    <row r="272" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D271">
+        <v>39.534100000000002</v>
+      </c>
+      <c r="E271">
+        <v>56.006300000000003</v>
+      </c>
+    </row>
+    <row r="272" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A272" s="4">
         <v>39264</v>
       </c>
@@ -3538,8 +4251,14 @@
       <c r="C272" s="5">
         <v>68.650088902999599</v>
       </c>
-    </row>
-    <row r="273" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D272">
+        <v>85.1892</v>
+      </c>
+      <c r="E272">
+        <v>66.429900000000004</v>
+      </c>
+    </row>
+    <row r="273" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A273" s="4">
         <v>39295</v>
       </c>
@@ -3549,8 +4268,14 @@
       <c r="C273" s="5">
         <v>80.227146599426703</v>
       </c>
-    </row>
-    <row r="274" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D273">
+        <v>88.45</v>
+      </c>
+      <c r="E273">
+        <v>62.874600000000001</v>
+      </c>
+    </row>
+    <row r="274" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A274" s="4">
         <v>39326</v>
       </c>
@@ -3560,8 +4285,14 @@
       <c r="C274" s="5">
         <v>60.725160042069803</v>
       </c>
-    </row>
-    <row r="275" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D274">
+        <v>83.163200000000003</v>
+      </c>
+      <c r="E274">
+        <v>54.533099999999997</v>
+      </c>
+    </row>
+    <row r="275" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A275" s="4">
         <v>39356</v>
       </c>
@@ -3571,8 +4302,14 @@
       <c r="C275" s="5">
         <v>73.640181655816505</v>
       </c>
-    </row>
-    <row r="276" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D275">
+        <v>104.0928</v>
+      </c>
+      <c r="E275">
+        <v>64.608800000000002</v>
+      </c>
+    </row>
+    <row r="276" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A276" s="4">
         <v>39387</v>
       </c>
@@ -3582,8 +4319,14 @@
       <c r="C276" s="5">
         <v>73.788584069978498</v>
       </c>
-    </row>
-    <row r="277" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D276">
+        <v>107.2063</v>
+      </c>
+      <c r="E276">
+        <v>48.229700000000001</v>
+      </c>
+    </row>
+    <row r="277" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A277" s="4">
         <v>39417</v>
       </c>
@@ -3593,8 +4336,14 @@
       <c r="C277" s="5">
         <v>57.993850355320397</v>
       </c>
-    </row>
-    <row r="278" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D277">
+        <v>81.542000000000002</v>
+      </c>
+      <c r="E277">
+        <v>63.144100000000002</v>
+      </c>
+    </row>
+    <row r="278" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A278" s="4">
         <v>39448</v>
       </c>
@@ -3604,8 +4353,14 @@
       <c r="C278" s="5">
         <v>93.720725220413698</v>
       </c>
-    </row>
-    <row r="279" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D278">
+        <v>123.96429999999999</v>
+      </c>
+      <c r="E278">
+        <v>56.727899999999998</v>
+      </c>
+    </row>
+    <row r="279" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A279" s="4">
         <v>39479</v>
       </c>
@@ -3615,8 +4370,14 @@
       <c r="C279" s="5">
         <v>58.8379480919982</v>
       </c>
-    </row>
-    <row r="280" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D279">
+        <v>69.138000000000005</v>
+      </c>
+      <c r="E279">
+        <v>67.374300000000005</v>
+      </c>
+    </row>
+    <row r="280" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A280" s="4">
         <v>39508</v>
       </c>
@@ -3626,8 +4387,14 @@
       <c r="C280" s="5">
         <v>64.027419429806002</v>
       </c>
-    </row>
-    <row r="281" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D280">
+        <v>86.682100000000005</v>
+      </c>
+      <c r="E280">
+        <v>77.655299999999997</v>
+      </c>
+    </row>
+    <row r="281" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A281" s="4">
         <v>39539</v>
       </c>
@@ -3637,8 +4404,14 @@
       <c r="C281" s="5">
         <v>53.051096921088401</v>
       </c>
-    </row>
-    <row r="282" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D281">
+        <v>89.812899999999999</v>
+      </c>
+      <c r="E281">
+        <v>47.791499999999999</v>
+      </c>
+    </row>
+    <row r="282" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A282" s="4">
         <v>39569</v>
       </c>
@@ -3648,8 +4421,14 @@
       <c r="C282" s="5">
         <v>49.275313562335597</v>
       </c>
-    </row>
-    <row r="283" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D282">
+        <v>117.3706</v>
+      </c>
+      <c r="E282">
+        <v>57.280799999999999</v>
+      </c>
+    </row>
+    <row r="283" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A283" s="4">
         <v>39600</v>
       </c>
@@ -3659,8 +4438,14 @@
       <c r="C283" s="5">
         <v>75.530725914895399</v>
       </c>
-    </row>
-    <row r="284" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D283">
+        <v>120.0471</v>
+      </c>
+      <c r="E283">
+        <v>69.449100000000001</v>
+      </c>
+    </row>
+    <row r="284" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A284" s="4">
         <v>39630</v>
       </c>
@@ -3670,8 +4455,14 @@
       <c r="C284" s="5">
         <v>63.187211596236502</v>
       </c>
-    </row>
-    <row r="285" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D284">
+        <v>108.4855</v>
+      </c>
+      <c r="E284">
+        <v>88.186999999999998</v>
+      </c>
+    </row>
+    <row r="285" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A285" s="4">
         <v>39661</v>
       </c>
@@ -3681,8 +4472,14 @@
       <c r="C285" s="5">
         <v>51.689010658757397</v>
       </c>
-    </row>
-    <row r="286" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D285">
+        <v>86.753200000000007</v>
+      </c>
+      <c r="E285">
+        <v>126.1512</v>
+      </c>
+    </row>
+    <row r="286" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A286" s="4">
         <v>39692</v>
       </c>
@@ -3692,8 +4489,14 @@
       <c r="C286" s="5">
         <v>96.223585935518599</v>
       </c>
-    </row>
-    <row r="287" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D286">
+        <v>97.499499999999998</v>
+      </c>
+      <c r="E286">
+        <v>70.260900000000007</v>
+      </c>
+    </row>
+    <row r="287" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A287" s="4">
         <v>39722</v>
       </c>
@@ -3703,8 +4506,14 @@
       <c r="C287" s="5">
         <v>75.326246154856193</v>
       </c>
-    </row>
-    <row r="288" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D287">
+        <v>34.628599999999999</v>
+      </c>
+      <c r="E287">
+        <v>75.357200000000006</v>
+      </c>
+    </row>
+    <row r="288" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A288" s="4">
         <v>39753</v>
       </c>
@@ -3714,8 +4523,14 @@
       <c r="C288" s="5">
         <v>141.957346108633</v>
       </c>
-    </row>
-    <row r="289" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D288">
+        <v>45.058900000000001</v>
+      </c>
+      <c r="E288">
+        <v>88.396000000000001</v>
+      </c>
+    </row>
+    <row r="289" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A289" s="4">
         <v>39783</v>
       </c>
@@ -3725,8 +4540,14 @@
       <c r="C289" s="5">
         <v>119.237736151676</v>
       </c>
-    </row>
-    <row r="290" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D289">
+        <v>66.289100000000005</v>
+      </c>
+      <c r="E289">
+        <v>75.647900000000007</v>
+      </c>
+    </row>
+    <row r="290" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A290" s="4">
         <v>39814</v>
       </c>
@@ -3736,8 +4557,14 @@
       <c r="C290" s="5">
         <v>96.352969607856195</v>
       </c>
-    </row>
-    <row r="291" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D290">
+        <v>77.511099999999999</v>
+      </c>
+      <c r="E290">
+        <v>49.526400000000002</v>
+      </c>
+    </row>
+    <row r="291" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A291" s="4">
         <v>39845</v>
       </c>
@@ -3747,8 +4574,14 @@
       <c r="C291" s="5">
         <v>47.421291449355301</v>
       </c>
-    </row>
-    <row r="292" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D291">
+        <v>45.090400000000002</v>
+      </c>
+      <c r="E291">
+        <v>57.3673</v>
+      </c>
+    </row>
+    <row r="292" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A292" s="4">
         <v>39873</v>
       </c>
@@ -3758,8 +4591,14 @@
       <c r="C292" s="5">
         <v>70.270837197154094</v>
       </c>
-    </row>
-    <row r="293" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D292">
+        <v>33.968299999999999</v>
+      </c>
+      <c r="E292">
+        <v>58.023699999999998</v>
+      </c>
+    </row>
+    <row r="293" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A293" s="4">
         <v>39904</v>
       </c>
@@ -3769,8 +4608,14 @@
       <c r="C293" s="5">
         <v>61.8700751656568</v>
       </c>
-    </row>
-    <row r="294" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D293">
+        <v>31.6967</v>
+      </c>
+      <c r="E293">
+        <v>81.450900000000004</v>
+      </c>
+    </row>
+    <row r="294" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A294" s="4">
         <v>39934</v>
       </c>
@@ -3780,8 +4625,14 @@
       <c r="C294" s="5">
         <v>86.758446055811504</v>
       </c>
-    </row>
-    <row r="295" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D294">
+        <v>30.2821</v>
+      </c>
+      <c r="E294">
+        <v>65.663499999999999</v>
+      </c>
+    </row>
+    <row r="295" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A295" s="4">
         <v>39965</v>
       </c>
@@ -3791,8 +4642,14 @@
       <c r="C295" s="5">
         <v>85.334957741957396</v>
       </c>
-    </row>
-    <row r="296" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D295">
+        <v>43.8857</v>
+      </c>
+      <c r="E295">
+        <v>55.679200000000002</v>
+      </c>
+    </row>
+    <row r="296" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A296" s="4">
         <v>39995</v>
       </c>
@@ -3802,8 +4659,14 @@
       <c r="C296" s="5">
         <v>64.417048850952497</v>
       </c>
-    </row>
-    <row r="297" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D296">
+        <v>51.184399999999997</v>
+      </c>
+      <c r="E296">
+        <v>67.038899999999998</v>
+      </c>
+    </row>
+    <row r="297" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A297" s="4">
         <v>40026</v>
       </c>
@@ -3813,8 +4676,14 @@
       <c r="C297" s="5">
         <v>69.223243512111196</v>
       </c>
-    </row>
-    <row r="298" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D297">
+        <v>34.018999999999998</v>
+      </c>
+      <c r="E297">
+        <v>69.968299999999999</v>
+      </c>
+    </row>
+    <row r="298" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A298" s="4">
         <v>40057</v>
       </c>
@@ -3824,8 +4693,14 @@
       <c r="C298" s="5">
         <v>68.224223720597195</v>
       </c>
-    </row>
-    <row r="299" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D298">
+        <v>24.612200000000001</v>
+      </c>
+      <c r="E298">
+        <v>39.844299999999997</v>
+      </c>
+    </row>
+    <row r="299" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A299" s="4">
         <v>40087</v>
       </c>
@@ -3835,8 +4710,14 @@
       <c r="C299" s="5">
         <v>113.297416798756</v>
       </c>
-    </row>
-    <row r="300" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D299">
+        <v>30.647099999999998</v>
+      </c>
+      <c r="E299">
+        <v>65.1524</v>
+      </c>
+    </row>
+    <row r="300" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A300" s="4">
         <v>40118</v>
       </c>
@@ -3846,8 +4727,14 @@
       <c r="C300" s="5">
         <v>72.574796865030294</v>
       </c>
-    </row>
-    <row r="301" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D300">
+        <v>29.205200000000001</v>
+      </c>
+      <c r="E300">
+        <v>26.265699999999999</v>
+      </c>
+    </row>
+    <row r="301" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A301" s="4">
         <v>40148</v>
       </c>
@@ -3857,8 +4744,14 @@
       <c r="C301" s="5">
         <v>50.897852355648801</v>
       </c>
-    </row>
-    <row r="302" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D301">
+        <v>83.447400000000002</v>
+      </c>
+      <c r="E301">
+        <v>74.842600000000004</v>
+      </c>
+    </row>
+    <row r="302" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A302" s="4">
         <v>40179</v>
       </c>
@@ -3868,8 +4761,14 @@
       <c r="C302" s="5">
         <v>36.487539842375099</v>
       </c>
-    </row>
-    <row r="303" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D302">
+        <v>82.325900000000004</v>
+      </c>
+      <c r="E302">
+        <v>67.514200000000002</v>
+      </c>
+    </row>
+    <row r="303" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A303" s="4">
         <v>40210</v>
       </c>
@@ -3879,8 +4778,14 @@
       <c r="C303" s="5">
         <v>33.610739635241202</v>
       </c>
-    </row>
-    <row r="304" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D303">
+        <v>51.798499999999997</v>
+      </c>
+      <c r="E303">
+        <v>37.145299999999999</v>
+      </c>
+    </row>
+    <row r="304" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A304" s="4">
         <v>40238</v>
       </c>
@@ -3890,8 +4795,14 @@
       <c r="C304" s="5">
         <v>53.995734031472303</v>
       </c>
-    </row>
-    <row r="305" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D304">
+        <v>45.201900000000002</v>
+      </c>
+      <c r="E304">
+        <v>39.903199999999998</v>
+      </c>
+    </row>
+    <row r="305" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A305" s="4">
         <v>40269</v>
       </c>
@@ -3901,8 +4812,14 @@
       <c r="C305" s="5">
         <v>89.260743220103905</v>
       </c>
-    </row>
-    <row r="306" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D305">
+        <v>42.553400000000003</v>
+      </c>
+      <c r="E305">
+        <v>61.7121</v>
+      </c>
+    </row>
+    <row r="306" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A306" s="4">
         <v>40299</v>
       </c>
@@ -3912,8 +4829,14 @@
       <c r="C306" s="5">
         <v>51.296880974234199</v>
       </c>
-    </row>
-    <row r="307" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D306">
+        <v>38.789700000000003</v>
+      </c>
+      <c r="E306">
+        <v>76.033699999999996</v>
+      </c>
+    </row>
+    <row r="307" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A307" s="4">
         <v>40330</v>
       </c>
@@ -3923,8 +4846,14 @@
       <c r="C307" s="5">
         <v>42.7274634323554</v>
       </c>
-    </row>
-    <row r="308" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D307">
+        <v>58.611800000000002</v>
+      </c>
+      <c r="E307">
+        <v>64.620400000000004</v>
+      </c>
+    </row>
+    <row r="308" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A308" s="4">
         <v>40360</v>
       </c>
@@ -3934,8 +4863,14 @@
       <c r="C308" s="5">
         <v>59.757928436600302</v>
       </c>
-    </row>
-    <row r="309" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D308">
+        <v>51.800199999999997</v>
+      </c>
+      <c r="E308">
+        <v>78.173699999999997</v>
+      </c>
+    </row>
+    <row r="309" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A309" s="4">
         <v>40391</v>
       </c>
@@ -3945,8 +4880,14 @@
       <c r="C309" s="5">
         <v>42.303438704420401</v>
       </c>
-    </row>
-    <row r="310" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D309">
+        <v>55.5276</v>
+      </c>
+      <c r="E309">
+        <v>57.033900000000003</v>
+      </c>
+    </row>
+    <row r="310" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A310" s="4">
         <v>40422</v>
       </c>
@@ -3956,8 +4897,14 @@
       <c r="C310" s="5">
         <v>34.935266871109697</v>
       </c>
-    </row>
-    <row r="311" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D310">
+        <v>58.205100000000002</v>
+      </c>
+      <c r="E310">
+        <v>38.985599999999998</v>
+      </c>
+    </row>
+    <row r="311" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A311" s="4">
         <v>40452</v>
       </c>
@@ -3967,8 +4914,14 @@
       <c r="C311" s="5">
         <v>29.646397357451299</v>
       </c>
-    </row>
-    <row r="312" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D311">
+        <v>66.916300000000007</v>
+      </c>
+      <c r="E311">
+        <v>47.8095</v>
+      </c>
+    </row>
+    <row r="312" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A312" s="4">
         <v>40483</v>
       </c>
@@ -3978,8 +4931,14 @@
       <c r="C312" s="5">
         <v>68.789031419330101</v>
       </c>
-    </row>
-    <row r="313" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D312">
+        <v>45.792000000000002</v>
+      </c>
+      <c r="E312">
+        <v>87.140799999999999</v>
+      </c>
+    </row>
+    <row r="313" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A313" s="4">
         <v>40513</v>
       </c>
@@ -3989,8 +4948,14 @@
       <c r="C313" s="5">
         <v>68.742895500674905</v>
       </c>
-    </row>
-    <row r="314" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D313">
+        <v>72.354100000000003</v>
+      </c>
+      <c r="E313">
+        <v>69.468900000000005</v>
+      </c>
+    </row>
+    <row r="314" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A314" s="4">
         <v>40544</v>
       </c>
@@ -4000,8 +4965,14 @@
       <c r="C314" s="5">
         <v>32.354130693964699</v>
       </c>
-    </row>
-    <row r="315" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D314">
+        <v>64.554500000000004</v>
+      </c>
+      <c r="E314">
+        <v>53.764899999999997</v>
+      </c>
+    </row>
+    <row r="315" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A315" s="4">
         <v>40575</v>
       </c>
@@ -4011,8 +4982,14 @@
       <c r="C315" s="5">
         <v>101.31718563001699</v>
       </c>
-    </row>
-    <row r="316" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D315">
+        <v>105.105</v>
+      </c>
+      <c r="E315">
+        <v>119.81959999999999</v>
+      </c>
+    </row>
+    <row r="316" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A316" s="4">
         <v>40603</v>
       </c>
@@ -4022,8 +4999,14 @@
       <c r="C316" s="5">
         <v>102.636287531901</v>
       </c>
-    </row>
-    <row r="317" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D316">
+        <v>244.48740000000001</v>
+      </c>
+      <c r="E316">
+        <v>217.76820000000001</v>
+      </c>
+    </row>
+    <row r="317" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A317" s="4">
         <v>40634</v>
       </c>
@@ -4033,8 +5016,14 @@
       <c r="C317" s="5">
         <v>69.457995483582195</v>
       </c>
-    </row>
-    <row r="318" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D317">
+        <v>81.872500000000002</v>
+      </c>
+      <c r="E317">
+        <v>145.05760000000001</v>
+      </c>
+    </row>
+    <row r="318" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A318" s="4">
         <v>40664</v>
       </c>
@@ -4044,8 +5033,14 @@
       <c r="C318" s="5">
         <v>83.713306146881493</v>
       </c>
-    </row>
-    <row r="319" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D318">
+        <v>78.161299999999997</v>
+      </c>
+      <c r="E318">
+        <v>96.500100000000003</v>
+      </c>
+    </row>
+    <row r="319" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A319" s="4">
         <v>40695</v>
       </c>
@@ -4055,8 +5050,14 @@
       <c r="C319" s="5">
         <v>33.716303856536399</v>
       </c>
-    </row>
-    <row r="320" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D319">
+        <v>87.290700000000001</v>
+      </c>
+      <c r="E319">
+        <v>61.925400000000003</v>
+      </c>
+    </row>
+    <row r="320" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A320" s="4">
         <v>40725</v>
       </c>
@@ -4066,8 +5067,14 @@
       <c r="C320" s="5">
         <v>104.73911122430199</v>
       </c>
-    </row>
-    <row r="321" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D320">
+        <v>61.8508</v>
+      </c>
+      <c r="E320">
+        <v>75.7089</v>
+      </c>
+    </row>
+    <row r="321" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A321" s="4">
         <v>40756</v>
       </c>
@@ -4077,8 +5084,14 @@
       <c r="C321" s="5">
         <v>79.101015587053396</v>
       </c>
-    </row>
-    <row r="322" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D321">
+        <v>94.353200000000001</v>
+      </c>
+      <c r="E321">
+        <v>123.8766</v>
+      </c>
+    </row>
+    <row r="322" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A322" s="4">
         <v>40787</v>
       </c>
@@ -4088,8 +5101,14 @@
       <c r="C322" s="5">
         <v>68.881050056539394</v>
       </c>
-    </row>
-    <row r="323" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D322">
+        <v>55.931399999999996</v>
+      </c>
+      <c r="E322">
+        <v>81.090599999999995</v>
+      </c>
+    </row>
+    <row r="323" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A323" s="4">
         <v>40817</v>
       </c>
@@ -4099,8 +5118,14 @@
       <c r="C323" s="5">
         <v>36.774988377189999</v>
       </c>
-    </row>
-    <row r="324" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D323">
+        <v>27.500599999999999</v>
+      </c>
+      <c r="E323">
+        <v>55.9666</v>
+      </c>
+    </row>
+    <row r="324" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A324" s="4">
         <v>40848</v>
       </c>
@@ -4110,8 +5135,14 @@
       <c r="C324" s="5">
         <v>85.441162740243996</v>
       </c>
-    </row>
-    <row r="325" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D324">
+        <v>71.780699999999996</v>
+      </c>
+      <c r="E324">
+        <v>87.496799999999993</v>
+      </c>
+    </row>
+    <row r="325" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A325" s="4">
         <v>40878</v>
       </c>
@@ -4121,8 +5152,14 @@
       <c r="C325" s="5">
         <v>102.400638689163</v>
       </c>
-    </row>
-    <row r="326" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D325">
+        <v>143.96549999999999</v>
+      </c>
+      <c r="E325">
+        <v>73.749899999999997</v>
+      </c>
+    </row>
+    <row r="326" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A326" s="4">
         <v>40909</v>
       </c>
@@ -4132,8 +5169,14 @@
       <c r="C326" s="5">
         <v>74.232606306725003</v>
       </c>
-    </row>
-    <row r="327" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D326">
+        <v>189.9436</v>
+      </c>
+      <c r="E326">
+        <v>84.942999999999998</v>
+      </c>
+    </row>
+    <row r="327" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A327" s="4">
         <v>40940</v>
       </c>
@@ -4143,8 +5186,14 @@
       <c r="C327" s="5">
         <v>40.366011316695101</v>
       </c>
-    </row>
-    <row r="328" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D327">
+        <v>125.0234</v>
+      </c>
+      <c r="E327">
+        <v>70.825400000000002</v>
+      </c>
+    </row>
+    <row r="328" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A328" s="4">
         <v>40969</v>
       </c>
@@ -4154,8 +5203,14 @@
       <c r="C328" s="5">
         <v>45.306411282954301</v>
       </c>
-    </row>
-    <row r="329" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D328">
+        <v>81.105699999999999</v>
+      </c>
+      <c r="E328">
+        <v>72.072299999999998</v>
+      </c>
+    </row>
+    <row r="329" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A329" s="4">
         <v>41000</v>
       </c>
@@ -4165,8 +5220,14 @@
       <c r="C329" s="5">
         <v>69.014628992472893</v>
       </c>
-    </row>
-    <row r="330" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D329">
+        <v>98.573499999999996</v>
+      </c>
+      <c r="E329">
+        <v>97.831100000000006</v>
+      </c>
+    </row>
+    <row r="330" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A330" s="4">
         <v>41030</v>
       </c>
@@ -4176,8 +5237,14 @@
       <c r="C330" s="5">
         <v>75.296919053034401</v>
       </c>
-    </row>
-    <row r="331" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D330">
+        <v>56.631100000000004</v>
+      </c>
+      <c r="E330">
+        <v>39.802</v>
+      </c>
+    </row>
+    <row r="331" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A331" s="4">
         <v>41061</v>
       </c>
@@ -4187,8 +5254,14 @@
       <c r="C331" s="5">
         <v>58.798605334987499</v>
       </c>
-    </row>
-    <row r="332" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D331">
+        <v>38.32</v>
+      </c>
+      <c r="E331">
+        <v>48.161499999999997</v>
+      </c>
+    </row>
+    <row r="332" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A332" s="4">
         <v>41091</v>
       </c>
@@ -4198,8 +5271,14 @@
       <c r="C332" s="5">
         <v>77.198617130963697</v>
       </c>
-    </row>
-    <row r="333" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D332">
+        <v>52.939500000000002</v>
+      </c>
+      <c r="E332">
+        <v>95.397999999999996</v>
+      </c>
+    </row>
+    <row r="333" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A333" s="4">
         <v>41122</v>
       </c>
@@ -4209,8 +5288,14 @@
       <c r="C333" s="5">
         <v>38.132044080662503</v>
       </c>
-    </row>
-    <row r="334" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D333">
+        <v>86.939400000000006</v>
+      </c>
+      <c r="E333">
+        <v>97.761700000000005</v>
+      </c>
+    </row>
+    <row r="334" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A334" s="4">
         <v>41153</v>
       </c>
@@ -4220,8 +5305,14 @@
       <c r="C334" s="5">
         <v>50.594913000055797</v>
       </c>
-    </row>
-    <row r="335" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D334">
+        <v>34.417000000000002</v>
+      </c>
+      <c r="E334">
+        <v>36.214799999999997</v>
+      </c>
+    </row>
+    <row r="335" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A335" s="4">
         <v>41183</v>
       </c>
@@ -4231,8 +5322,14 @@
       <c r="C335" s="5">
         <v>60.623874480297999</v>
       </c>
-    </row>
-    <row r="336" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D335">
+        <v>52.655900000000003</v>
+      </c>
+      <c r="E335">
+        <v>81.369799999999998</v>
+      </c>
+    </row>
+    <row r="336" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A336" s="4">
         <v>41214</v>
       </c>
@@ -4242,8 +5339,14 @@
       <c r="C336" s="5">
         <v>60.310214572028997</v>
       </c>
-    </row>
-    <row r="337" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D336">
+        <v>52.011299999999999</v>
+      </c>
+      <c r="E336">
+        <v>62.582099999999997</v>
+      </c>
+    </row>
+    <row r="337" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A337" s="4">
         <v>41244</v>
       </c>
@@ -4253,8 +5356,14 @@
       <c r="C337" s="5">
         <v>33.958098558044199</v>
       </c>
-    </row>
-    <row r="338" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D337">
+        <v>38.008899999999997</v>
+      </c>
+      <c r="E337">
+        <v>64.374799999999993</v>
+      </c>
+    </row>
+    <row r="338" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A338" s="4">
         <v>41275</v>
       </c>
@@ -4264,8 +5373,14 @@
       <c r="C338" s="5">
         <v>54.180922105838</v>
       </c>
-    </row>
-    <row r="339" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D338">
+        <v>64.714200000000005</v>
+      </c>
+      <c r="E338">
+        <v>45.822499999999998</v>
+      </c>
+    </row>
+    <row r="339" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A339" s="4">
         <v>41306</v>
       </c>
@@ -4275,8 +5390,14 @@
       <c r="C339" s="5">
         <v>59.7795425119442</v>
       </c>
-    </row>
-    <row r="340" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D339">
+        <v>50.804200000000002</v>
+      </c>
+      <c r="E339">
+        <v>55.332700000000003</v>
+      </c>
+    </row>
+    <row r="340" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A340" s="4">
         <v>41334</v>
       </c>
@@ -4286,8 +5407,14 @@
       <c r="C340" s="5">
         <v>66.245063046010301</v>
       </c>
-    </row>
-    <row r="341" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D340">
+        <v>28.380199999999999</v>
+      </c>
+      <c r="E340">
+        <v>44.530299999999997</v>
+      </c>
+    </row>
+    <row r="341" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A341" s="4">
         <v>41365</v>
       </c>
@@ -4297,8 +5424,14 @@
       <c r="C341" s="5">
         <v>67.215064423864902</v>
       </c>
-    </row>
-    <row r="342" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D341">
+        <v>42.365699999999997</v>
+      </c>
+      <c r="E341">
+        <v>56.5976</v>
+      </c>
+    </row>
+    <row r="342" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A342" s="4">
         <v>41395</v>
       </c>
@@ -4308,8 +5441,14 @@
       <c r="C342" s="5">
         <v>34.779310839961397</v>
       </c>
-    </row>
-    <row r="343" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D342">
+        <v>30.125399999999999</v>
+      </c>
+      <c r="E342">
+        <v>52.454799999999999</v>
+      </c>
+    </row>
+    <row r="343" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A343" s="4">
         <v>41426</v>
       </c>
@@ -4319,8 +5458,14 @@
       <c r="C343" s="5">
         <v>46.604462690741499</v>
       </c>
-    </row>
-    <row r="344" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D343">
+        <v>46.188299999999998</v>
+      </c>
+      <c r="E343">
+        <v>32.375300000000003</v>
+      </c>
+    </row>
+    <row r="344" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A344" s="4">
         <v>41456</v>
       </c>
@@ -4330,8 +5475,14 @@
       <c r="C344" s="5">
         <v>68.455284042755196</v>
       </c>
-    </row>
-    <row r="345" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D344">
+        <v>44.904499999999999</v>
+      </c>
+      <c r="E344">
+        <v>106.51049999999999</v>
+      </c>
+    </row>
+    <row r="345" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A345" s="4">
         <v>41487</v>
       </c>
@@ -4341,8 +5492,14 @@
       <c r="C345" s="5">
         <v>85.607026325151693</v>
       </c>
-    </row>
-    <row r="346" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D345">
+        <v>87.739500000000007</v>
+      </c>
+      <c r="E345">
+        <v>96.598500000000001</v>
+      </c>
+    </row>
+    <row r="346" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A346" s="4">
         <v>41518</v>
       </c>
@@ -4352,8 +5509,14 @@
       <c r="C346" s="5">
         <v>56.827906253416899</v>
       </c>
-    </row>
-    <row r="347" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D346">
+        <v>76.878600000000006</v>
+      </c>
+      <c r="E346">
+        <v>33.020699999999998</v>
+      </c>
+    </row>
+    <row r="347" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A347" s="4">
         <v>41548</v>
       </c>
@@ -4363,8 +5526,14 @@
       <c r="C347" s="5">
         <v>63.205362046798797</v>
       </c>
-    </row>
-    <row r="348" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D347">
+        <v>35.7376</v>
+      </c>
+      <c r="E347">
+        <v>45.073300000000003</v>
+      </c>
+    </row>
+    <row r="348" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A348" s="4">
         <v>41579</v>
       </c>
@@ -4374,8 +5543,14 @@
       <c r="C348" s="5">
         <v>44.586153529456197</v>
       </c>
-    </row>
-    <row r="349" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D348">
+        <v>77.991100000000003</v>
+      </c>
+      <c r="E348">
+        <v>51.622399999999999</v>
+      </c>
+    </row>
+    <row r="349" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A349" s="4">
         <v>41609</v>
       </c>
@@ -4385,8 +5560,14 @@
       <c r="C349" s="5">
         <v>71.432750302262804</v>
       </c>
-    </row>
-    <row r="350" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D349">
+        <v>60.831600000000002</v>
+      </c>
+      <c r="E349">
+        <v>96.917699999999996</v>
+      </c>
+    </row>
+    <row r="350" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A350" s="4">
         <v>41640</v>
       </c>
@@ -4396,8 +5577,14 @@
       <c r="C350" s="5">
         <v>80.877648835505497</v>
       </c>
-    </row>
-    <row r="351" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D350">
+        <v>41.806399999999996</v>
+      </c>
+      <c r="E350">
+        <v>54.189500000000002</v>
+      </c>
+    </row>
+    <row r="351" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A351" s="4">
         <v>41671</v>
       </c>
@@ -4407,8 +5594,14 @@
       <c r="C351" s="5">
         <v>43.496109887283701</v>
       </c>
-    </row>
-    <row r="352" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D351">
+        <v>31.005400000000002</v>
+      </c>
+      <c r="E351">
+        <v>107.74169999999999</v>
+      </c>
+    </row>
+    <row r="352" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A352" s="4">
         <v>41699</v>
       </c>
@@ -4418,8 +5611,14 @@
       <c r="C352" s="5">
         <v>108.44819856351501</v>
       </c>
-    </row>
-    <row r="353" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D352">
+        <v>103.1126</v>
+      </c>
+      <c r="E352">
+        <v>131.07939999999999</v>
+      </c>
+    </row>
+    <row r="353" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A353" s="4">
         <v>41730</v>
       </c>
@@ -4429,8 +5628,14 @@
       <c r="C353" s="5">
         <v>69.5495399138522</v>
       </c>
-    </row>
-    <row r="354" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D353">
+        <v>117.4234</v>
+      </c>
+      <c r="E353">
+        <v>90.803899999999999</v>
+      </c>
+    </row>
+    <row r="354" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A354" s="4">
         <v>41760</v>
       </c>
@@ -4440,8 +5645,14 @@
       <c r="C354" s="5">
         <v>73.271146173262096</v>
       </c>
-    </row>
-    <row r="355" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D354">
+        <v>89.740300000000005</v>
+      </c>
+      <c r="E354">
+        <v>49.705800000000004</v>
+      </c>
+    </row>
+    <row r="355" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A355" s="4">
         <v>41791</v>
       </c>
@@ -4451,8 +5662,14 @@
       <c r="C355" s="5">
         <v>60.158504911581197</v>
       </c>
-    </row>
-    <row r="356" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D355">
+        <v>84.859399999999994</v>
+      </c>
+      <c r="E355">
+        <v>58.705199999999998</v>
+      </c>
+    </row>
+    <row r="356" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A356" s="4">
         <v>41821</v>
       </c>
@@ -4462,8 +5679,14 @@
       <c r="C356" s="5">
         <v>108.76882710401399</v>
       </c>
-    </row>
-    <row r="357" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D356">
+        <v>131.50409999999999</v>
+      </c>
+      <c r="E356">
+        <v>207.42330000000001</v>
+      </c>
+    </row>
+    <row r="357" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A357" s="4">
         <v>41852</v>
       </c>
@@ -4473,8 +5696,14 @@
       <c r="C357" s="5">
         <v>157.48826093007</v>
       </c>
-    </row>
-    <row r="358" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D357">
+        <v>160.07409999999999</v>
+      </c>
+      <c r="E357">
+        <v>346.84750000000003</v>
+      </c>
+    </row>
+    <row r="358" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A358" s="4">
         <v>41883</v>
       </c>
@@ -4484,8 +5713,14 @@
       <c r="C358" s="5">
         <v>98.959013186527102</v>
       </c>
-    </row>
-    <row r="359" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D358">
+        <v>104.82640000000001</v>
+      </c>
+      <c r="E358">
+        <v>201.11660000000001</v>
+      </c>
+    </row>
+    <row r="359" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A359" s="4">
         <v>41913</v>
       </c>
@@ -4495,8 +5730,14 @@
       <c r="C359" s="5">
         <v>117.505742596316</v>
       </c>
-    </row>
-    <row r="360" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D359">
+        <v>65.902699999999996</v>
+      </c>
+      <c r="E359">
+        <v>125.9773</v>
+      </c>
+    </row>
+    <row r="360" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A360" s="4">
         <v>41944</v>
       </c>
@@ -4506,8 +5747,14 @@
       <c r="C360" s="5">
         <v>84.164950899080694</v>
       </c>
-    </row>
-    <row r="361" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D360">
+        <v>55.177399999999999</v>
+      </c>
+      <c r="E360">
+        <v>133.05850000000001</v>
+      </c>
+    </row>
+    <row r="361" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A361" s="4">
         <v>41974</v>
       </c>
@@ -4517,8 +5764,14 @@
       <c r="C361" s="5">
         <v>96.3072515026509</v>
       </c>
-    </row>
-    <row r="362" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D361">
+        <v>89.513999999999996</v>
+      </c>
+      <c r="E361">
+        <v>144.38720000000001</v>
+      </c>
+    </row>
+    <row r="362" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A362" s="4">
         <v>42005</v>
       </c>
@@ -4528,8 +5781,14 @@
       <c r="C362" s="5">
         <v>64.457573579284499</v>
       </c>
-    </row>
-    <row r="363" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D362">
+        <v>57.496400000000001</v>
+      </c>
+      <c r="E362">
+        <v>69.725700000000003</v>
+      </c>
+    </row>
+    <row r="363" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A363" s="4">
         <v>42036</v>
       </c>
@@ -4539,8 +5798,14 @@
       <c r="C363" s="5">
         <v>81.511504946532796</v>
       </c>
-    </row>
-    <row r="364" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D363">
+        <v>66.786299999999997</v>
+      </c>
+      <c r="E363">
+        <v>80.230099999999993</v>
+      </c>
+    </row>
+    <row r="364" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A364" s="4">
         <v>42064</v>
       </c>
@@ -4550,8 +5815,14 @@
       <c r="C364" s="5">
         <v>76.132890860510898</v>
       </c>
-    </row>
-    <row r="365" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D364">
+        <v>56.945</v>
+      </c>
+      <c r="E364">
+        <v>92.534999999999997</v>
+      </c>
+    </row>
+    <row r="365" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A365" s="4">
         <v>42095</v>
       </c>
@@ -4561,8 +5832,14 @@
       <c r="C365" s="5">
         <v>53.632961856390402</v>
       </c>
-    </row>
-    <row r="366" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D365">
+        <v>68.808700000000002</v>
+      </c>
+      <c r="E365">
+        <v>101.9646</v>
+      </c>
+    </row>
+    <row r="366" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A366" s="4">
         <v>42125</v>
       </c>
@@ -4572,8 +5849,14 @@
       <c r="C366" s="5">
         <v>90.738478849836099</v>
       </c>
-    </row>
-    <row r="367" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D366">
+        <v>26.8096</v>
+      </c>
+      <c r="E366">
+        <v>58.151400000000002</v>
+      </c>
+    </row>
+    <row r="367" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A367" s="4">
         <v>42156</v>
       </c>
@@ -4583,8 +5866,14 @@
       <c r="C367" s="5">
         <v>59.195649215230198</v>
       </c>
-    </row>
-    <row r="368" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D367">
+        <v>60.576099999999997</v>
+      </c>
+      <c r="E367">
+        <v>122.8062</v>
+      </c>
+    </row>
+    <row r="368" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A368" s="4">
         <v>42186</v>
       </c>
@@ -4594,8 +5883,14 @@
       <c r="C368" s="5">
         <v>84.895757155220394</v>
       </c>
-    </row>
-    <row r="369" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D368">
+        <v>61.891599999999997</v>
+      </c>
+      <c r="E368">
+        <v>75.795400000000001</v>
+      </c>
+    </row>
+    <row r="369" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A369" s="4">
         <v>42217</v>
       </c>
@@ -4605,8 +5900,14 @@
       <c r="C369" s="5">
         <v>59.6078681109882</v>
       </c>
-    </row>
-    <row r="370" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D369">
+        <v>63.9499</v>
+      </c>
+      <c r="E369">
+        <v>98.515799999999999</v>
+      </c>
+    </row>
+    <row r="370" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A370" s="4">
         <v>42248</v>
       </c>
@@ -4616,8 +5917,14 @@
       <c r="C370" s="5">
         <v>50.419132943025602</v>
       </c>
-    </row>
-    <row r="371" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D370">
+        <v>29.1083</v>
+      </c>
+      <c r="E370">
+        <v>56.630800000000001</v>
+      </c>
+    </row>
+    <row r="371" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A371" s="4">
         <v>42278</v>
       </c>
@@ -4627,8 +5934,14 @@
       <c r="C371" s="5">
         <v>70.773447189734796</v>
       </c>
-    </row>
-    <row r="372" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D371">
+        <v>36.822200000000002</v>
+      </c>
+      <c r="E371">
+        <v>95.871099999999998</v>
+      </c>
+    </row>
+    <row r="372" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A372" s="4">
         <v>42309</v>
       </c>
@@ -4638,8 +5951,14 @@
       <c r="C372" s="5">
         <v>125.79706590875701</v>
       </c>
-    </row>
-    <row r="373" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D372">
+        <v>89.293400000000005</v>
+      </c>
+      <c r="E372">
+        <v>307.35289999999998</v>
+      </c>
+    </row>
+    <row r="373" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A373" s="4">
         <v>42339</v>
       </c>
@@ -4649,8 +5968,14 @@
       <c r="C373" s="5">
         <v>59.757741324324698</v>
       </c>
-    </row>
-    <row r="374" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D373">
+        <v>37.614899999999999</v>
+      </c>
+      <c r="E373">
+        <v>113.30500000000001</v>
+      </c>
+    </row>
+    <row r="374" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A374" s="4">
         <v>42370</v>
       </c>
@@ -4660,8 +5985,14 @@
       <c r="C374" s="5">
         <v>125.949402136053</v>
       </c>
-    </row>
-    <row r="375" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D374">
+        <v>78.884600000000006</v>
+      </c>
+      <c r="E374">
+        <v>222.57060000000001</v>
+      </c>
+    </row>
+    <row r="375" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A375" s="4">
         <v>42401</v>
       </c>
@@ -4671,8 +6002,14 @@
       <c r="C375" s="5">
         <v>55.009643552495099</v>
       </c>
-    </row>
-    <row r="376" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D375">
+        <v>58.180599999999998</v>
+      </c>
+      <c r="E375">
+        <v>122.31059999999999</v>
+      </c>
+    </row>
+    <row r="376" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A376" s="4">
         <v>42430</v>
       </c>
@@ -4682,8 +6019,14 @@
       <c r="C376" s="5">
         <v>99.717693799032304</v>
       </c>
-    </row>
-    <row r="377" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D376">
+        <v>51.293599999999998</v>
+      </c>
+      <c r="E376">
+        <v>180.1985</v>
+      </c>
+    </row>
+    <row r="377" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A377" s="4">
         <v>42461</v>
       </c>
@@ -4693,8 +6036,14 @@
       <c r="C377" s="5">
         <v>62.652602812093598</v>
       </c>
-    </row>
-    <row r="378" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D377">
+        <v>33.794899999999998</v>
+      </c>
+      <c r="E377">
+        <v>102.22839999999999</v>
+      </c>
+    </row>
+    <row r="378" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A378" s="4">
         <v>42491</v>
       </c>
@@ -4704,8 +6053,14 @@
       <c r="C378" s="5">
         <v>68.962825646440805</v>
       </c>
-    </row>
-    <row r="379" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D378">
+        <v>54.155799999999999</v>
+      </c>
+      <c r="E378">
+        <v>88.135199999999998</v>
+      </c>
+    </row>
+    <row r="379" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A379" s="4">
         <v>42522</v>
       </c>
@@ -4715,8 +6070,14 @@
       <c r="C379" s="5">
         <v>89.404272815808994</v>
       </c>
-    </row>
-    <row r="380" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D379">
+        <v>44.5045</v>
+      </c>
+      <c r="E379">
+        <v>77.754199999999997</v>
+      </c>
+    </row>
+    <row r="380" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A380" s="4">
         <v>42552</v>
       </c>
@@ -4726,8 +6087,14 @@
       <c r="C380" s="5">
         <v>120.44064783234801</v>
       </c>
-    </row>
-    <row r="381" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D380">
+        <v>64.585800000000006</v>
+      </c>
+      <c r="E380">
+        <v>191.0284</v>
+      </c>
+    </row>
+    <row r="381" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A381" s="4">
         <v>42583</v>
       </c>
@@ -4737,8 +6104,14 @@
       <c r="C381" s="5">
         <v>50.931862407915503</v>
       </c>
-    </row>
-    <row r="382" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D381">
+        <v>64.337400000000002</v>
+      </c>
+      <c r="E381">
+        <v>88.278300000000002</v>
+      </c>
+    </row>
+    <row r="382" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A382" s="4">
         <v>42614</v>
       </c>
@@ -4748,8 +6121,14 @@
       <c r="C382" s="5">
         <v>64.460880762091904</v>
       </c>
-    </row>
-    <row r="383" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D382">
+        <v>57.097999999999999</v>
+      </c>
+      <c r="E382">
+        <v>91.911900000000003</v>
+      </c>
+    </row>
+    <row r="383" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A383" s="4">
         <v>42644</v>
       </c>
@@ -4759,8 +6138,14 @@
       <c r="C383" s="5">
         <v>49.2263948524078</v>
       </c>
-    </row>
-    <row r="384" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D383">
+        <v>66.738600000000005</v>
+      </c>
+      <c r="E383">
+        <v>86.467500000000001</v>
+      </c>
+    </row>
+    <row r="384" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A384" s="4">
         <v>42675</v>
       </c>
@@ -4770,8 +6155,14 @@
       <c r="C384" s="5">
         <v>74.114215683894898</v>
       </c>
-    </row>
-    <row r="385" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D384">
+        <v>52.522500000000001</v>
+      </c>
+      <c r="E384">
+        <v>68.258200000000002</v>
+      </c>
+    </row>
+    <row r="385" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A385" s="4">
         <v>42705</v>
       </c>
@@ -4781,8 +6172,14 @@
       <c r="C385" s="5">
         <v>55.138958970085099</v>
       </c>
-    </row>
-    <row r="386" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D385">
+        <v>66.213499999999996</v>
+      </c>
+      <c r="E385">
+        <v>78.364699999999999</v>
+      </c>
+    </row>
+    <row r="386" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A386" s="4">
         <v>42736</v>
       </c>
@@ -4792,8 +6189,14 @@
       <c r="C386" s="5">
         <v>83.982017029891296</v>
       </c>
-    </row>
-    <row r="387" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D386">
+        <v>49.713000000000001</v>
+      </c>
+      <c r="E386">
+        <v>43.470399999999998</v>
+      </c>
+    </row>
+    <row r="387" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A387" s="4">
         <v>42767</v>
       </c>
@@ -4803,8 +6206,14 @@
       <c r="C387" s="5">
         <v>100.168736123507</v>
       </c>
-    </row>
-    <row r="388" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D387">
+        <v>63.078200000000002</v>
+      </c>
+      <c r="E387">
+        <v>64.443899999999999</v>
+      </c>
+    </row>
+    <row r="388" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A388" s="4">
         <v>42795</v>
       </c>
@@ -4814,8 +6223,14 @@
       <c r="C388" s="5">
         <v>52.228841838077898</v>
       </c>
-    </row>
-    <row r="389" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D388">
+        <v>67.025999999999996</v>
+      </c>
+      <c r="E388">
+        <v>40.560600000000001</v>
+      </c>
+    </row>
+    <row r="389" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A389" s="4">
         <v>42826</v>
       </c>
@@ -4825,8 +6240,14 @@
       <c r="C389" s="5">
         <v>84.376808298950294</v>
       </c>
-    </row>
-    <row r="390" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D389">
+        <v>57.861899999999999</v>
+      </c>
+      <c r="E389">
+        <v>114.2525</v>
+      </c>
+    </row>
+    <row r="390" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A390" s="4">
         <v>42856</v>
       </c>
@@ -4836,8 +6257,14 @@
       <c r="C390" s="5">
         <v>38.921217193221601</v>
       </c>
-    </row>
-    <row r="391" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D390">
+        <v>38.060400000000001</v>
+      </c>
+      <c r="E390">
+        <v>51.356900000000003</v>
+      </c>
+    </row>
+    <row r="391" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A391" s="4">
         <v>42887</v>
       </c>
@@ -4847,8 +6274,14 @@
       <c r="C391" s="5">
         <v>132.607023490926</v>
       </c>
-    </row>
-    <row r="392" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D391">
+        <v>66.107900000000001</v>
+      </c>
+      <c r="E391">
+        <v>89.656999999999996</v>
+      </c>
+    </row>
+    <row r="392" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A392" s="4">
         <v>42917</v>
       </c>
@@ -4858,8 +6291,14 @@
       <c r="C392" s="5">
         <v>62.723481316620202</v>
       </c>
-    </row>
-    <row r="393" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D392">
+        <v>34.463799999999999</v>
+      </c>
+      <c r="E392">
+        <v>85.164299999999997</v>
+      </c>
+    </row>
+    <row r="393" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A393" s="4">
         <v>42948</v>
       </c>
@@ -4869,8 +6308,14 @@
       <c r="C393" s="5">
         <v>119.01814500849601</v>
       </c>
-    </row>
-    <row r="394" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D393">
+        <v>52.185600000000001</v>
+      </c>
+      <c r="E393">
+        <v>115.91030000000001</v>
+      </c>
+    </row>
+    <row r="394" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A394" s="4">
         <v>42979</v>
       </c>
@@ -4880,8 +6325,14 @@
       <c r="C394" s="5">
         <v>66.679102178343996</v>
       </c>
-    </row>
-    <row r="395" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D394">
+        <v>96.567400000000006</v>
+      </c>
+      <c r="E394">
+        <v>66.209299999999999</v>
+      </c>
+    </row>
+    <row r="395" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A395" s="4">
         <v>43009</v>
       </c>
@@ -4891,8 +6342,14 @@
       <c r="C395" s="5">
         <v>80.508440852173294</v>
       </c>
-    </row>
-    <row r="396" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D395">
+        <v>58.960900000000002</v>
+      </c>
+      <c r="E395">
+        <v>72.980599999999995</v>
+      </c>
+    </row>
+    <row r="396" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A396" s="4">
         <v>43040</v>
       </c>
@@ -4902,8 +6359,14 @@
       <c r="C396" s="5">
         <v>42.313970523290003</v>
       </c>
-    </row>
-    <row r="397" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D396">
+        <v>58.085099999999997</v>
+      </c>
+      <c r="E396">
+        <v>57.965000000000003</v>
+      </c>
+    </row>
+    <row r="397" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A397" s="4">
         <v>43070</v>
       </c>
@@ -4913,8 +6376,14 @@
       <c r="C397" s="5">
         <v>60.467742434509198</v>
       </c>
-    </row>
-    <row r="398" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D397">
+        <v>104.5198</v>
+      </c>
+      <c r="E397">
+        <v>63.153599999999997</v>
+      </c>
+    </row>
+    <row r="398" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A398" s="4">
         <v>43101</v>
       </c>
@@ -4924,8 +6393,14 @@
       <c r="C398" s="5">
         <v>53.924765873225098</v>
       </c>
-    </row>
-    <row r="399" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D398">
+        <v>62.799799999999998</v>
+      </c>
+      <c r="E398">
+        <v>79.214200000000005</v>
+      </c>
+    </row>
+    <row r="399" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A399" s="4">
         <v>43132</v>
       </c>
@@ -4935,8 +6410,14 @@
       <c r="C399" s="5">
         <v>36.644659235460303</v>
       </c>
-    </row>
-    <row r="400" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D399">
+        <v>51.275599999999997</v>
+      </c>
+      <c r="E399">
+        <v>53.598799999999997</v>
+      </c>
+    </row>
+    <row r="400" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A400" s="4">
         <v>43160</v>
       </c>
@@ -4946,8 +6427,14 @@
       <c r="C400" s="5">
         <v>51.285122043166197</v>
       </c>
-    </row>
-    <row r="401" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D400">
+        <v>48.731000000000002</v>
+      </c>
+      <c r="E400">
+        <v>57.769199999999998</v>
+      </c>
+    </row>
+    <row r="401" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A401" s="4">
         <v>43191</v>
       </c>
@@ -4957,8 +6444,14 @@
       <c r="C401" s="5">
         <v>94.432579731679596</v>
       </c>
-    </row>
-    <row r="402" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D401">
+        <v>68.158199999999994</v>
+      </c>
+      <c r="E401">
+        <v>95.924899999999994</v>
+      </c>
+    </row>
+    <row r="402" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A402" s="4">
         <v>43221</v>
       </c>
@@ -4968,8 +6461,14 @@
       <c r="C402" s="5">
         <v>65.837094007709695</v>
       </c>
-    </row>
-    <row r="403" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D402">
+        <v>83.260999999999996</v>
+      </c>
+      <c r="E402">
+        <v>81.611500000000007</v>
+      </c>
+    </row>
+    <row r="403" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A403" s="4">
         <v>43252</v>
       </c>
@@ -4979,8 +6478,14 @@
       <c r="C403" s="5">
         <v>83.434892043302796</v>
       </c>
-    </row>
-    <row r="404" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D403">
+        <v>73.374200000000002</v>
+      </c>
+      <c r="E403">
+        <v>77.727900000000005</v>
+      </c>
+    </row>
+    <row r="404" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A404" s="4">
         <v>43282</v>
       </c>
@@ -4990,8 +6495,14 @@
       <c r="C404" s="5">
         <v>65.7263168974075</v>
       </c>
-    </row>
-    <row r="405" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D404">
+        <v>62.098799999999997</v>
+      </c>
+      <c r="E404">
+        <v>63.823</v>
+      </c>
+    </row>
+    <row r="405" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A405" s="4">
         <v>43313</v>
       </c>
@@ -5001,8 +6512,14 @@
       <c r="C405" s="5">
         <v>119.32277187575301</v>
       </c>
-    </row>
-    <row r="406" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D405">
+        <v>95.224999999999994</v>
+      </c>
+      <c r="E405">
+        <v>128.12129999999999</v>
+      </c>
+    </row>
+    <row r="406" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A406" s="4">
         <v>43344</v>
       </c>
@@ -5012,8 +6529,14 @@
       <c r="C406" s="5">
         <v>63.751105070780099</v>
       </c>
-    </row>
-    <row r="407" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D406">
+        <v>61.008299999999998</v>
+      </c>
+      <c r="E406">
+        <v>80.866799999999998</v>
+      </c>
+    </row>
+    <row r="407" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A407" s="4">
         <v>43374</v>
       </c>
@@ -5023,8 +6546,14 @@
       <c r="C407" s="5">
         <v>109.331689454122</v>
       </c>
-    </row>
-    <row r="408" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D407">
+        <v>58.919600000000003</v>
+      </c>
+      <c r="E407">
+        <v>81.993099999999998</v>
+      </c>
+    </row>
+    <row r="408" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A408" s="4">
         <v>43405</v>
       </c>
@@ -5034,8 +6563,14 @@
       <c r="C408" s="5">
         <v>64.572690871656704</v>
       </c>
-    </row>
-    <row r="409" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D408">
+        <v>77.910300000000007</v>
+      </c>
+      <c r="E408">
+        <v>88.956100000000006</v>
+      </c>
+    </row>
+    <row r="409" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A409" s="4">
         <v>43435</v>
       </c>
@@ -5045,8 +6580,14 @@
       <c r="C409" s="5">
         <v>122.574037095818</v>
       </c>
-    </row>
-    <row r="410" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D409">
+        <v>50.181399999999996</v>
+      </c>
+      <c r="E409">
+        <v>135.56700000000001</v>
+      </c>
+    </row>
+    <row r="410" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A410" s="4">
         <v>43466</v>
       </c>
@@ -5056,8 +6597,14 @@
       <c r="C410" s="5">
         <v>97.258548054047296</v>
       </c>
-    </row>
-    <row r="411" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D410">
+        <v>75.373699999999999</v>
+      </c>
+      <c r="E410">
+        <v>62.447400000000002</v>
+      </c>
+    </row>
+    <row r="411" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A411" s="4">
         <v>43497</v>
       </c>
@@ -5067,8 +6614,14 @@
       <c r="C411" s="5">
         <v>64.025553102694005</v>
       </c>
-    </row>
-    <row r="412" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D411">
+        <v>96.872</v>
+      </c>
+      <c r="E411">
+        <v>60.3063</v>
+      </c>
+    </row>
+    <row r="412" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A412" s="4">
         <v>43525</v>
       </c>
@@ -5078,8 +6631,14 @@
       <c r="C412" s="5">
         <v>51.827523050181497</v>
       </c>
-    </row>
-    <row r="413" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D412">
+        <v>52.722299999999997</v>
+      </c>
+      <c r="E412">
+        <v>49.069400000000002</v>
+      </c>
+    </row>
+    <row r="413" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A413" s="4">
         <v>43556</v>
       </c>
@@ -5089,8 +6648,14 @@
       <c r="C413" s="5">
         <v>62.968846503833703</v>
       </c>
-    </row>
-    <row r="414" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D413">
+        <v>83.988200000000006</v>
+      </c>
+      <c r="E413">
+        <v>84.015299999999996</v>
+      </c>
+    </row>
+    <row r="414" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A414" s="4">
         <v>43586</v>
       </c>
@@ -5100,8 +6665,14 @@
       <c r="C414" s="5">
         <v>36.768168360958697</v>
       </c>
-    </row>
-    <row r="415" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D414">
+        <v>89.124700000000004</v>
+      </c>
+      <c r="E414">
+        <v>98.576999999999998</v>
+      </c>
+    </row>
+    <row r="415" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A415" s="4">
         <v>43617</v>
       </c>
@@ -5111,8 +6682,14 @@
       <c r="C415" s="5">
         <v>78.478330397042598</v>
       </c>
-    </row>
-    <row r="416" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D415">
+        <v>104.4171</v>
+      </c>
+      <c r="E415">
+        <v>81.990600000000001</v>
+      </c>
+    </row>
+    <row r="416" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A416" s="4">
         <v>43647</v>
       </c>
@@ -5122,8 +6699,14 @@
       <c r="C416" s="5">
         <v>86.978794764448907</v>
       </c>
-    </row>
-    <row r="417" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D416">
+        <v>54.592399999999998</v>
+      </c>
+      <c r="E416">
+        <v>96.188400000000001</v>
+      </c>
+    </row>
+    <row r="417" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A417" s="4">
         <v>43678</v>
       </c>
@@ -5133,8 +6716,14 @@
       <c r="C417" s="5">
         <v>129.265604904225</v>
       </c>
-    </row>
-    <row r="418" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D417">
+        <v>59.998199999999997</v>
+      </c>
+      <c r="E417">
+        <v>120.72629999999999</v>
+      </c>
+    </row>
+    <row r="418" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A418" s="4">
         <v>43709</v>
       </c>
@@ -5144,8 +6733,14 @@
       <c r="C418" s="5">
         <v>68.554416104005</v>
       </c>
-    </row>
-    <row r="419" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D418">
+        <v>163.61930000000001</v>
+      </c>
+      <c r="E418">
+        <v>48.288600000000002</v>
+      </c>
+    </row>
+    <row r="419" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A419" s="4">
         <v>43739</v>
       </c>
@@ -5155,8 +6750,14 @@
       <c r="C419" s="5">
         <v>176.21003814094399</v>
       </c>
-    </row>
-    <row r="420" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D419">
+        <v>86.899500000000003</v>
+      </c>
+      <c r="E419">
+        <v>140.52449999999999</v>
+      </c>
+    </row>
+    <row r="420" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A420" s="4">
         <v>43770</v>
       </c>
@@ -5166,8 +6767,14 @@
       <c r="C420" s="5">
         <v>81.313653426676595</v>
       </c>
-    </row>
-    <row r="421" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D420">
+        <v>61.318600000000004</v>
+      </c>
+      <c r="E420">
+        <v>61.899099999999997</v>
+      </c>
+    </row>
+    <row r="421" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A421" s="4">
         <v>43800</v>
       </c>
@@ -5177,8 +6784,14 @@
       <c r="C421" s="5">
         <v>79.418907253928396</v>
       </c>
-    </row>
-    <row r="422" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D421">
+        <v>50.576300000000003</v>
+      </c>
+      <c r="E421">
+        <v>80.918999999999997</v>
+      </c>
+    </row>
+    <row r="422" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A422" s="4">
         <v>43831</v>
       </c>
@@ -5188,8 +6801,14 @@
       <c r="C422" s="5">
         <v>108.638885091239</v>
       </c>
-    </row>
-    <row r="423" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D422">
+        <v>141.1559</v>
+      </c>
+      <c r="E422">
+        <v>96.501800000000003</v>
+      </c>
+    </row>
+    <row r="423" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A423" s="4">
         <v>43862</v>
       </c>
@@ -5199,8 +6818,14 @@
       <c r="C423" s="5">
         <v>73.459813926187493</v>
       </c>
-    </row>
-    <row r="424" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D423">
+        <v>57.421999999999997</v>
+      </c>
+      <c r="E423">
+        <v>125.1721</v>
+      </c>
+    </row>
+    <row r="424" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A424" s="4">
         <v>43891</v>
       </c>
@@ -5210,8 +6835,14 @@
       <c r="C424" s="5">
         <v>276.66203951383102</v>
       </c>
-    </row>
-    <row r="425" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D424">
+        <v>80.480800000000002</v>
+      </c>
+      <c r="E424">
+        <v>259.54270000000002</v>
+      </c>
+    </row>
+    <row r="425" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A425" s="4">
         <v>43922</v>
       </c>
@@ -5221,8 +6852,14 @@
       <c r="C425" s="5">
         <v>168.481373711077</v>
       </c>
-    </row>
-    <row r="426" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D425">
+        <v>60.745399999999997</v>
+      </c>
+      <c r="E425">
+        <v>123.1417</v>
+      </c>
+    </row>
+    <row r="426" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A426" s="4">
         <v>43952</v>
       </c>
@@ -5232,8 +6869,14 @@
       <c r="C426" s="5">
         <v>150.39878366779101</v>
       </c>
-    </row>
-    <row r="427" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D426">
+        <v>36.781100000000002</v>
+      </c>
+      <c r="E426">
+        <v>89.722099999999998</v>
+      </c>
+    </row>
+    <row r="427" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A427" s="4">
         <v>43983</v>
       </c>
@@ -5243,8 +6886,14 @@
       <c r="C427" s="5">
         <v>74.926178406669706</v>
       </c>
-    </row>
-    <row r="428" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D427">
+        <v>45.625300000000003</v>
+      </c>
+      <c r="E427">
+        <v>98.766599999999997</v>
+      </c>
+    </row>
+    <row r="428" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A428" s="4">
         <v>44013</v>
       </c>
@@ -5254,8 +6903,14 @@
       <c r="C428" s="5">
         <v>87.889442760683494</v>
       </c>
-    </row>
-    <row r="429" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D428">
+        <v>40.526000000000003</v>
+      </c>
+      <c r="E428">
+        <v>103.0245</v>
+      </c>
+    </row>
+    <row r="429" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A429" s="4">
         <v>44044</v>
       </c>
@@ -5265,8 +6920,14 @@
       <c r="C429" s="5">
         <v>93.577527032665898</v>
       </c>
-    </row>
-    <row r="430" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D429">
+        <v>41.432499999999997</v>
+      </c>
+      <c r="E429">
+        <v>132.18639999999999</v>
+      </c>
+    </row>
+    <row r="430" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A430" s="4">
         <v>44075</v>
       </c>
@@ -5276,8 +6937,14 @@
       <c r="C430" s="5">
         <v>42.926924537468302</v>
       </c>
-    </row>
-    <row r="431" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D430">
+        <v>27.715800000000002</v>
+      </c>
+      <c r="E430">
+        <v>79.596900000000005</v>
+      </c>
+    </row>
+    <row r="431" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A431" s="4">
         <v>44105</v>
       </c>
@@ -5287,8 +6954,14 @@
       <c r="C431" s="5">
         <v>63.416422435229798</v>
       </c>
-    </row>
-    <row r="432" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D431">
+        <v>30.441500000000001</v>
+      </c>
+      <c r="E431">
+        <v>117.8867</v>
+      </c>
+    </row>
+    <row r="432" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A432" s="4">
         <v>44136</v>
       </c>
@@ -5298,8 +6971,14 @@
       <c r="C432" s="5">
         <v>73.219466401559799</v>
       </c>
-    </row>
-    <row r="433" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D432">
+        <v>38.096299999999999</v>
+      </c>
+      <c r="E432">
+        <v>77.317300000000003</v>
+      </c>
+    </row>
+    <row r="433" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A433" s="4">
         <v>44166</v>
       </c>
@@ -5309,8 +6988,14 @@
       <c r="C433" s="5">
         <v>70.226075364251699</v>
       </c>
-    </row>
-    <row r="434" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D433">
+        <v>42.992600000000003</v>
+      </c>
+      <c r="E433">
+        <v>50.534199999999998</v>
+      </c>
+    </row>
+    <row r="434" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A434" s="4">
         <v>44197</v>
       </c>
@@ -5320,8 +7005,14 @@
       <c r="C434" s="5">
         <v>81.388460299691005</v>
       </c>
-    </row>
-    <row r="435" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D434">
+        <v>63.975900000000003</v>
+      </c>
+      <c r="E434">
+        <v>56.138399999999997</v>
+      </c>
+    </row>
+    <row r="435" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A435" s="4">
         <v>44228</v>
       </c>
@@ -5331,8 +7022,14 @@
       <c r="C435" s="5">
         <v>89.723854344931397</v>
       </c>
-    </row>
-    <row r="436" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D435">
+        <v>37.279800000000002</v>
+      </c>
+      <c r="E435">
+        <v>89.297300000000007</v>
+      </c>
+    </row>
+    <row r="436" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A436" s="4">
         <v>44256</v>
       </c>
@@ -5342,8 +7039,14 @@
       <c r="C436" s="5">
         <v>81.227534777957601</v>
       </c>
-    </row>
-    <row r="437" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D436">
+        <v>67.005300000000005</v>
+      </c>
+      <c r="E436">
+        <v>58.732500000000002</v>
+      </c>
+    </row>
+    <row r="437" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A437" s="4">
         <v>44287</v>
       </c>
@@ -5353,8 +7056,14 @@
       <c r="C437" s="5">
         <v>44.9105651528008</v>
       </c>
-    </row>
-    <row r="438" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D437">
+        <v>46.788899999999998</v>
+      </c>
+      <c r="E437">
+        <v>80.367099999999994</v>
+      </c>
+    </row>
+    <row r="438" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A438" s="4">
         <v>44317</v>
       </c>
@@ -5364,8 +7073,14 @@
       <c r="C438" s="5">
         <v>74.7641333600357</v>
       </c>
-    </row>
-    <row r="439" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D438">
+        <v>49.343600000000002</v>
+      </c>
+      <c r="E438">
+        <v>79.796400000000006</v>
+      </c>
+    </row>
+    <row r="439" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A439" s="4">
         <v>44348</v>
       </c>
@@ -5375,8 +7090,14 @@
       <c r="C439" s="5">
         <v>57.832730081109098</v>
       </c>
-    </row>
-    <row r="440" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D439">
+        <v>52.198700000000002</v>
+      </c>
+      <c r="E439">
+        <v>35.6083</v>
+      </c>
+    </row>
+    <row r="440" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A440" s="4">
         <v>44378</v>
       </c>
@@ -5386,8 +7107,14 @@
       <c r="C440" s="5">
         <v>96.647143001039296</v>
       </c>
-    </row>
-    <row r="441" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D440">
+        <v>45.452599999999997</v>
+      </c>
+      <c r="E440">
+        <v>68.837199999999996</v>
+      </c>
+    </row>
+    <row r="441" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A441" s="4">
         <v>44409</v>
       </c>
@@ -5397,8 +7124,14 @@
       <c r="C441" s="5">
         <v>209.037162505499</v>
       </c>
-    </row>
-    <row r="442" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D441">
+        <v>64.912999999999997</v>
+      </c>
+      <c r="E441">
+        <v>91.252899999999997</v>
+      </c>
+    </row>
+    <row r="442" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A442" s="4">
         <v>44440</v>
       </c>
@@ -5408,8 +7141,14 @@
       <c r="C442" s="5">
         <v>56.580869603195097</v>
       </c>
-    </row>
-    <row r="443" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D442">
+        <v>81.270499999999998</v>
+      </c>
+      <c r="E442">
+        <v>78.619600000000005</v>
+      </c>
+    </row>
+    <row r="443" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A443" s="4">
         <v>44470</v>
       </c>
@@ -5419,8 +7158,14 @@
       <c r="C443" s="5">
         <v>66.190639239765503</v>
       </c>
-    </row>
-    <row r="444" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D443">
+        <v>123.4872</v>
+      </c>
+      <c r="E443">
+        <v>61.881</v>
+      </c>
+    </row>
+    <row r="444" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A444" s="4">
         <v>44501</v>
       </c>
@@ -5430,8 +7175,14 @@
       <c r="C444" s="5">
         <v>65.8389775836159</v>
       </c>
-    </row>
-    <row r="445" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D444">
+        <v>94.812299999999993</v>
+      </c>
+      <c r="E444">
+        <v>91.819500000000005</v>
+      </c>
+    </row>
+    <row r="445" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A445" s="4">
         <v>44531</v>
       </c>
@@ -5441,8 +7192,14 @@
       <c r="C445" s="5">
         <v>52.412330665418203</v>
       </c>
-    </row>
-    <row r="446" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D445">
+        <v>100.2069</v>
+      </c>
+      <c r="E445">
+        <v>65.838399999999993</v>
+      </c>
+    </row>
+    <row r="446" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A446" s="4">
         <v>44562</v>
       </c>
@@ -5452,8 +7209,14 @@
       <c r="C446" s="5">
         <v>114.09789065619999</v>
       </c>
-    </row>
-    <row r="447" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D446">
+        <v>190.2842</v>
+      </c>
+      <c r="E446">
+        <v>98.850399999999993</v>
+      </c>
+    </row>
+    <row r="447" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A447" s="4">
         <v>44593</v>
       </c>
@@ -5463,8 +7226,14 @@
       <c r="C447" s="5">
         <v>193.61078594151101</v>
       </c>
-    </row>
-    <row r="448" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D447">
+        <v>529.57119999999998</v>
+      </c>
+      <c r="E447">
+        <v>304.98610000000002</v>
+      </c>
+    </row>
+    <row r="448" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A448" s="4">
         <v>44621</v>
       </c>
@@ -5474,8 +7243,14 @@
       <c r="C448" s="5">
         <v>334.43389834659303</v>
       </c>
-    </row>
-    <row r="449" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D448" s="6">
+        <v>1085.5</v>
+      </c>
+      <c r="E448">
+        <v>421.30889999999999</v>
+      </c>
+    </row>
+    <row r="449" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A449" s="4">
         <v>44652</v>
       </c>
@@ -5485,8 +7260,14 @@
       <c r="C449" s="5">
         <v>175.47482673983001</v>
       </c>
-    </row>
-    <row r="450" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D449">
+        <v>567.94479999999999</v>
+      </c>
+      <c r="E449">
+        <v>273.9477</v>
+      </c>
+    </row>
+    <row r="450" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A450" s="4">
         <v>44682</v>
       </c>
@@ -5496,8 +7277,14 @@
       <c r="C450" s="5">
         <v>87.849750005437002</v>
       </c>
-    </row>
-    <row r="451" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D450">
+        <v>477.90550000000002</v>
+      </c>
+      <c r="E450">
+        <v>156.95689999999999</v>
+      </c>
+    </row>
+    <row r="451" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A451" s="4">
         <v>44713</v>
       </c>
@@ -5507,8 +7294,14 @@
       <c r="C451" s="5">
         <v>99.959145530221207</v>
       </c>
-    </row>
-    <row r="452" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D451">
+        <v>387.15249999999997</v>
+      </c>
+      <c r="E451">
+        <v>112.63720000000001</v>
+      </c>
+    </row>
+    <row r="452" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A452" s="4">
         <v>44743</v>
       </c>
@@ -5518,8 +7311,14 @@
       <c r="C452" s="5">
         <v>115.648301636621</v>
       </c>
-    </row>
-    <row r="453" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D452">
+        <v>344.23070000000001</v>
+      </c>
+      <c r="E452">
+        <v>145.5967</v>
+      </c>
+    </row>
+    <row r="453" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A453" s="4">
         <v>44774</v>
       </c>
@@ -5529,8 +7328,14 @@
       <c r="C453" s="5">
         <v>105.98065907711199</v>
       </c>
-    </row>
-    <row r="454" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D453">
+        <v>394.70350000000002</v>
+      </c>
+      <c r="E453">
+        <v>181.12970000000001</v>
+      </c>
+    </row>
+    <row r="454" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A454" s="4">
         <v>44805</v>
       </c>
@@ -5540,8 +7345,14 @@
       <c r="C454" s="5">
         <v>98.254274463799703</v>
       </c>
-    </row>
-    <row r="455" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D454">
+        <v>366.06889999999999</v>
+      </c>
+      <c r="E454">
+        <v>116.4781</v>
+      </c>
+    </row>
+    <row r="455" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A455" s="4">
         <v>44835</v>
       </c>
@@ -5551,8 +7362,14 @@
       <c r="C455" s="5">
         <v>121.267724892926</v>
       </c>
-    </row>
-    <row r="456" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D455">
+        <v>311.40350000000001</v>
+      </c>
+      <c r="E455">
+        <v>164.96979999999999</v>
+      </c>
+    </row>
+    <row r="456" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A456" s="4">
         <v>44866</v>
       </c>
@@ -5562,8 +7379,14 @@
       <c r="C456" s="5">
         <v>94.294452818476699</v>
       </c>
-    </row>
-    <row r="457" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D456">
+        <v>216.4795</v>
+      </c>
+      <c r="E456">
+        <v>90.204899999999995</v>
+      </c>
+    </row>
+    <row r="457" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A457" s="4">
         <v>44896</v>
       </c>
@@ -5573,8 +7396,14 @@
       <c r="C457" s="5">
         <v>73.497950052543501</v>
       </c>
-    </row>
-    <row r="458" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D457">
+        <v>273.02929999999998</v>
+      </c>
+      <c r="E457">
+        <v>91.396600000000007</v>
+      </c>
+    </row>
+    <row r="458" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A458" s="4">
         <v>44927</v>
       </c>
@@ -5584,8 +7413,14 @@
       <c r="C458" s="5">
         <v>57.411711674643797</v>
       </c>
-    </row>
-    <row r="459" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D458">
+        <v>193.14580000000001</v>
+      </c>
+      <c r="E458">
+        <v>125.27160000000001</v>
+      </c>
+    </row>
+    <row r="459" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A459" s="4">
         <v>44958</v>
       </c>
@@ -5595,8 +7430,14 @@
       <c r="C459" s="5">
         <v>90.948855704032596</v>
       </c>
-    </row>
-    <row r="460" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D459">
+        <v>136.88890000000001</v>
+      </c>
+      <c r="E459">
+        <v>83.194000000000003</v>
+      </c>
+    </row>
+    <row r="460" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A460" s="4">
         <v>44986</v>
       </c>
@@ -5606,8 +7447,14 @@
       <c r="C460" s="5">
         <v>52.632507698143201</v>
       </c>
-    </row>
-    <row r="461" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D460">
+        <v>129.44810000000001</v>
+      </c>
+      <c r="E460">
+        <v>95.428899999999999</v>
+      </c>
+    </row>
+    <row r="461" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A461" s="4">
         <v>45017</v>
       </c>
@@ -5617,8 +7464,14 @@
       <c r="C461" s="5">
         <v>93.593854984116405</v>
       </c>
-    </row>
-    <row r="462" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D461">
+        <v>137.2594</v>
+      </c>
+      <c r="E461">
+        <v>68.330100000000002</v>
+      </c>
+    </row>
+    <row r="462" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A462" s="4">
         <v>45047</v>
       </c>
@@ -5628,8 +7481,14 @@
       <c r="C462" s="5">
         <v>98.915966690812695</v>
       </c>
-    </row>
-    <row r="463" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D462">
+        <v>95.984099999999998</v>
+      </c>
+      <c r="E462">
+        <v>93.246799999999993</v>
+      </c>
+    </row>
+    <row r="463" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A463" s="4">
         <v>45078</v>
       </c>
@@ -5639,8 +7498,14 @@
       <c r="C463" s="5">
         <v>75.491790015818594</v>
       </c>
-    </row>
-    <row r="464" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D463">
+        <v>99.763199999999998</v>
+      </c>
+      <c r="E463">
+        <v>108.9239</v>
+      </c>
+    </row>
+    <row r="464" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A464" s="4">
         <v>45108</v>
       </c>
@@ -5650,8 +7515,14 @@
       <c r="C464" s="5">
         <v>60.192564661107497</v>
       </c>
-    </row>
-    <row r="465" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D464">
+        <v>152.76150000000001</v>
+      </c>
+      <c r="E464">
+        <v>83.975300000000004</v>
+      </c>
+    </row>
+    <row r="465" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A465" s="4">
         <v>45139</v>
       </c>
@@ -5661,8 +7532,14 @@
       <c r="C465" s="5">
         <v>147.747058984235</v>
       </c>
-    </row>
-    <row r="466" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D465">
+        <v>159.51660000000001</v>
+      </c>
+      <c r="E465">
+        <v>122.17059999999999</v>
+      </c>
+    </row>
+    <row r="466" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A466" s="4">
         <v>45170</v>
       </c>
@@ -5672,8 +7549,14 @@
       <c r="C466" s="5">
         <v>74.738697148687393</v>
       </c>
-    </row>
-    <row r="467" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D466">
+        <v>90.832400000000007</v>
+      </c>
+      <c r="E466">
+        <v>99.561300000000003</v>
+      </c>
+    </row>
+    <row r="467" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A467" s="4">
         <v>45200</v>
       </c>
@@ -5683,8 +7566,14 @@
       <c r="C467" s="5">
         <v>181.08444273288299</v>
       </c>
-    </row>
-    <row r="468" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D467">
+        <v>222.672</v>
+      </c>
+      <c r="E467">
+        <v>205.38310000000001</v>
+      </c>
+    </row>
+    <row r="468" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A468" s="4">
         <v>45231</v>
       </c>
@@ -5694,8 +7583,14 @@
       <c r="C468" s="5">
         <v>172.23369179590901</v>
       </c>
-    </row>
-    <row r="469" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D468">
+        <v>152.6163</v>
+      </c>
+      <c r="E468">
+        <v>139.06370000000001</v>
+      </c>
+    </row>
+    <row r="469" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A469" s="4">
         <v>45261</v>
       </c>
@@ -5705,8 +7600,14 @@
       <c r="C469" s="5">
         <v>130.68245251029799</v>
       </c>
-    </row>
-    <row r="470" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D469">
+        <v>178.46090000000001</v>
+      </c>
+      <c r="E469">
+        <v>115.8708</v>
+      </c>
+    </row>
+    <row r="470" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A470" s="4">
         <v>45292</v>
       </c>
@@ -5716,8 +7617,14 @@
       <c r="C470" s="5">
         <v>136.73506543284299</v>
       </c>
-    </row>
-    <row r="471" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D470">
+        <v>229.51300000000001</v>
+      </c>
+      <c r="E470">
+        <v>189.5104</v>
+      </c>
+    </row>
+    <row r="471" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A471" s="4">
         <v>45323</v>
       </c>
@@ -5727,8 +7634,14 @@
       <c r="C471" s="5">
         <v>168.60544629460301</v>
       </c>
-    </row>
-    <row r="472" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D471">
+        <v>169.3023</v>
+      </c>
+      <c r="E471">
+        <v>192.27090000000001</v>
+      </c>
+    </row>
+    <row r="472" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A472" s="4">
         <v>45352</v>
       </c>
@@ -5738,8 +7651,14 @@
       <c r="C472" s="5">
         <v>136.204527452495</v>
       </c>
-    </row>
-    <row r="473" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D472">
+        <v>155.2439</v>
+      </c>
+      <c r="E472">
+        <v>132.9597</v>
+      </c>
+    </row>
+    <row r="473" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A473" s="4">
         <v>45383</v>
       </c>
@@ -5749,8 +7668,14 @@
       <c r="C473" s="5">
         <v>173.756780279411</v>
       </c>
-    </row>
-    <row r="474" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D473">
+        <v>162.32900000000001</v>
+      </c>
+      <c r="E473">
+        <v>97.286000000000001</v>
+      </c>
+    </row>
+    <row r="474" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A474" s="4">
         <v>45413</v>
       </c>
@@ -5760,8 +7685,14 @@
       <c r="C474" s="5">
         <v>134.33060297528399</v>
       </c>
-    </row>
-    <row r="475" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D474">
+        <v>129.1497</v>
+      </c>
+      <c r="E474">
+        <v>93.224299999999999</v>
+      </c>
+    </row>
+    <row r="475" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A475" s="4">
         <v>45444</v>
       </c>
@@ -5771,8 +7702,14 @@
       <c r="C475" s="5">
         <v>94.544718594222203</v>
       </c>
-    </row>
-    <row r="476" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D475">
+        <v>117.3635</v>
+      </c>
+      <c r="E475">
+        <v>74.226299999999995</v>
+      </c>
+    </row>
+    <row r="476" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A476" s="4">
         <v>45474</v>
       </c>
@@ -5782,8 +7719,14 @@
       <c r="C476" s="5">
         <v>101.409856118314</v>
       </c>
-    </row>
-    <row r="477" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D476">
+        <v>111.7137</v>
+      </c>
+      <c r="E476">
+        <v>91.188900000000004</v>
+      </c>
+    </row>
+    <row r="477" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A477" s="4">
         <v>45505</v>
       </c>
@@ -5793,8 +7736,14 @@
       <c r="C477" s="5">
         <v>128.70290171536101</v>
       </c>
-    </row>
-    <row r="478" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D477">
+        <v>162.48759999999999</v>
+      </c>
+      <c r="E477">
+        <v>145.87350000000001</v>
+      </c>
+    </row>
+    <row r="478" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A478" s="4">
         <v>45536</v>
       </c>
@@ -5804,8 +7753,14 @@
       <c r="C478" s="5">
         <v>140.962587824336</v>
       </c>
-    </row>
-    <row r="479" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D478">
+        <v>94.016199999999998</v>
+      </c>
+      <c r="E478">
+        <v>151.74160000000001</v>
+      </c>
+    </row>
+    <row r="479" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A479" s="4">
         <v>45566</v>
       </c>
@@ -5815,8 +7770,14 @@
       <c r="C479" s="5">
         <v>134.30668219385001</v>
       </c>
-    </row>
-    <row r="480" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D479">
+        <v>149.8116</v>
+      </c>
+      <c r="E479">
+        <v>150.56720000000001</v>
+      </c>
+    </row>
+    <row r="480" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A480" s="4">
         <v>45597</v>
       </c>
@@ -5826,8 +7787,14 @@
       <c r="C480" s="5">
         <v>87.228828358379701</v>
       </c>
-    </row>
-    <row r="481" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D480">
+        <v>161.46600000000001</v>
+      </c>
+      <c r="E480">
+        <v>141.83070000000001</v>
+      </c>
+    </row>
+    <row r="481" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A481" s="4">
         <v>45627</v>
       </c>
@@ -5837,8 +7804,14 @@
       <c r="C481" s="5">
         <v>83.734800909262802</v>
       </c>
-    </row>
-    <row r="482" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D481">
+        <v>180.53550000000001</v>
+      </c>
+      <c r="E481">
+        <v>117.5705</v>
+      </c>
+    </row>
+    <row r="482" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A482" s="4">
         <v>45658</v>
       </c>
@@ -5848,8 +7821,14 @@
       <c r="C482" s="5">
         <v>75.294848150343896</v>
       </c>
-    </row>
-    <row r="483" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D482">
+        <v>147.9759</v>
+      </c>
+      <c r="E482">
+        <v>129.4325</v>
+      </c>
+    </row>
+    <row r="483" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A483" s="4">
         <v>45689</v>
       </c>
@@ -5859,8 +7838,14 @@
       <c r="C483" s="5">
         <v>180.702923540591</v>
       </c>
-    </row>
-    <row r="484" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D483">
+        <v>173.35679999999999</v>
+      </c>
+      <c r="E483">
+        <v>112.8409</v>
+      </c>
+    </row>
+    <row r="484" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A484" s="4">
         <v>45717</v>
       </c>
@@ -5870,8 +7855,14 @@
       <c r="C484" s="5">
         <v>236.49297068375401</v>
       </c>
-    </row>
-    <row r="485" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D484">
+        <v>280.90800000000002</v>
+      </c>
+      <c r="E484">
+        <v>200.92689999999999</v>
+      </c>
+    </row>
+    <row r="485" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A485" s="4">
         <v>45748</v>
       </c>
@@ -5881,8 +7872,14 @@
       <c r="C485" s="5">
         <v>230.282906842263</v>
       </c>
-    </row>
-    <row r="486" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D485">
+        <v>205.85249999999999</v>
+      </c>
+      <c r="E485">
+        <v>202.0752</v>
+      </c>
+    </row>
+    <row r="486" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A486" s="4">
         <v>45778</v>
       </c>
@@ -5892,8 +7889,14 @@
       <c r="C486" s="5">
         <v>145.82317293499699</v>
       </c>
-    </row>
-    <row r="487" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D486">
+        <v>206.39400000000001</v>
+      </c>
+      <c r="E486">
+        <v>161.9864</v>
+      </c>
+    </row>
+    <row r="487" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A487" s="4">
         <v>45809</v>
       </c>
@@ -5903,8 +7906,14 @@
       <c r="C487" s="5">
         <v>170.01513157791101</v>
       </c>
-    </row>
-    <row r="488" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D487">
+        <v>382.2287</v>
+      </c>
+      <c r="E487">
+        <v>161.4111</v>
+      </c>
+    </row>
+    <row r="488" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A488" s="4">
         <v>45839</v>
       </c>
@@ -5914,8 +7923,14 @@
       <c r="C488" s="5">
         <v>155.29201398511299</v>
       </c>
-    </row>
-    <row r="489" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D488">
+        <v>292.63260000000002</v>
+      </c>
+      <c r="E488">
+        <v>197.66900000000001</v>
+      </c>
+    </row>
+    <row r="489" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A489" s="4">
         <v>45870</v>
       </c>
@@ -5925,8 +7940,14 @@
       <c r="C489" s="5">
         <v>163.00216992171099</v>
       </c>
-    </row>
-    <row r="490" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D489">
+        <v>200.5247</v>
+      </c>
+      <c r="E489">
+        <v>118.10899999999999</v>
+      </c>
+    </row>
+    <row r="490" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A490" s="4">
         <v>45901</v>
       </c>
@@ -5936,8 +7957,14 @@
       <c r="C490" s="5">
         <v>105.472401635563</v>
       </c>
-    </row>
-    <row r="491" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D490">
+        <v>151.00479999999999</v>
+      </c>
+      <c r="E490">
+        <v>111.0877</v>
+      </c>
+    </row>
+    <row r="491" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A491" s="4">
         <v>45931</v>
       </c>
@@ -5947,8 +7974,14 @@
       <c r="C491" s="5">
         <v>124.468900343562</v>
       </c>
-    </row>
-    <row r="492" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D491">
+        <v>186.92439999999999</v>
+      </c>
+      <c r="E491">
+        <v>92.900099999999995</v>
+      </c>
+    </row>
+    <row r="492" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A492" s="4">
         <v>45962</v>
       </c>
@@ -5958,8 +7991,14 @@
       <c r="C492" s="5">
         <v>91.452596202965594</v>
       </c>
-    </row>
-    <row r="493" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D492">
+        <v>144.9992</v>
+      </c>
+      <c r="E492">
+        <v>138.06020000000001</v>
+      </c>
+    </row>
+    <row r="493" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A493" s="4">
         <v>45992</v>
       </c>
@@ -5969,8 +8008,14 @@
       <c r="C493" s="5">
         <v>107.269851195309</v>
       </c>
-    </row>
-    <row r="494" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D493">
+        <v>180.32149999999999</v>
+      </c>
+      <c r="E493">
+        <v>98.568299999999994</v>
+      </c>
+    </row>
+    <row r="494" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A494" s="4">
         <v>46023</v>
       </c>
@@ -5980,8 +8025,14 @@
       <c r="C494" s="5">
         <v>118.271893067116</v>
       </c>
-    </row>
-    <row r="495" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D494">
+        <v>246.97370000000001</v>
+      </c>
+      <c r="E494">
+        <v>207.7354</v>
+      </c>
+    </row>
+    <row r="495" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A495" s="4">
         <v>46054</v>
       </c>
@@ -5991,8 +8042,14 @@
       <c r="C495" s="5">
         <v>45.875807748856197</v>
       </c>
-    </row>
-    <row r="496" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D495">
+        <v>185.32210000000001</v>
+      </c>
+      <c r="E495">
+        <v>145.9736</v>
+      </c>
+    </row>
+    <row r="496" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A496" s="4">
         <v>46082</v>
       </c>
@@ -6001,6 +8058,12 @@
       </c>
       <c r="C496" s="5">
         <v>217.289026630916</v>
+      </c>
+      <c r="D496" s="6">
+        <v>1422.1</v>
+      </c>
+      <c r="E496">
+        <v>251.02379999999999</v>
       </c>
     </row>
   </sheetData>
